--- a/Revalidacion Moose Scorpion Gecko/RA_GECKO.xlsx
+++ b/Revalidacion Moose Scorpion Gecko/RA_GECKO.xlsx
@@ -6395,7 +6395,7 @@
     <row r="2" spans="1:19" s="20" customFormat="1" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A2" s="145" t="inlineStr">
         <is>
-          <t xml:space="preserve">Estaciones GECKO de Atornillado Automático (VSS1H-6050-001 a 006, MS-550-001, MS-550-002)</t>
+          <t xml:space="preserve">REVALIDACION: Estaciones GECKO de Atornillado Automático (VSS1H-6050-001 a 006, MS-550-001, MS-550-002)</t>
         </is>
       </c>
       <c r="B2" s="127"/>
@@ -6435,7 +6435,7 @@
       <c r="C3" s="127"/>
       <c r="D3" s="52" t="inlineStr">
         <is>
-          <t xml:space="preserve">18/09/2026</t>
+          <t xml:space="preserve">30/09/2026</t>
         </is>
       </c>
       <c r="E3" s="143" t="s">
@@ -6606,12 +6606,12 @@
       </c>
       <c r="B8" s="55" t="inlineStr">
         <is>
-          <t xml:space="preserve">Operación normal - carga de pieza con robot gantry en posición de reposo</t>
+          <t xml:space="preserve">Carga de pieza en la fixtura y clampeo manual</t>
         </is>
       </c>
       <c r="C8" s="56" t="inlineStr">
         <is>
-          <t xml:space="preserve">El operador coloca la pieza manualmente en la fixtura, la clampea con los 2 clamps y sale del área antes de dar avance</t>
+          <t xml:space="preserve">Paso 1 de 2: el operador coloca la pieza manualmente en la fixtura, en posición de reposo del gantry</t>
         </is>
       </c>
       <c r="D8" s="56" t="inlineStr">
@@ -6655,12 +6655,19 @@
       </c>
       <c r="L8" s="58" t="inlineStr">
         <is>
-          <t xml:space="preserve">No se requiere EPP adicional; el control es por cortinas de seguridad en el área central.</t>
+          <t xml:space="preserve">Bata/gorro de cuarto limpio (cleanroom), guantes de nitrilo, lentes de seguridad y calzado antiestático (ESD), conforme al ingreso a Cuarto Limpio ISO 7.</t>
         </is>
       </c>
       <c r="M8" s="58" t="inlineStr">
         <is>
-          <t xml:space="preserve">SOP Operación Estaciones GECKO</t>
+          <t xml:space="preserve">16-AT40-3318-00013
+16-AT40-3318-00014
+16-AT40-3318-00015
+16-AT40-3318-00016
+16-AT40-3318-00017
+16-AT40-3318-00018
+16-AT40-3318-00019
+16-AT40-3318-00020</t>
         </is>
       </c>
       <c r="N8" s="57" t="inlineStr">
@@ -6692,42 +6699,42 @@
       </c>
       <c r="B9" s="55" t="inlineStr">
         <is>
-          <t xml:space="preserve">Operación normal - movimiento del slider en X (y eje adicional en algunas estaciones)</t>
+          <t xml:space="preserve">Carga de pieza en la fixtura y clampeo manual</t>
         </is>
       </c>
       <c r="C9" s="56" t="inlineStr">
         <is>
-          <t xml:space="preserve">El slider mueve la fixtura con la pieza clampeada hacia la posición de atornillado durante el ciclo automático</t>
+          <t xml:space="preserve">Paso 2 de 2: cierra los 2 clamps manuales de la fixtura y sale del área antes de dar avance</t>
         </is>
       </c>
       <c r="D9" s="56" t="inlineStr">
         <is>
-          <t xml:space="preserve">Mecanico</t>
+          <t xml:space="preserve">Ergonomía</t>
         </is>
       </c>
       <c r="E9" s="49" t="inlineStr">
         <is>
-          <t xml:space="preserve">Partes móviles</t>
+          <t xml:space="preserve">Movimientos repetitivos</t>
         </is>
       </c>
       <c r="F9" s="49" t="inlineStr">
         <is>
-          <t xml:space="preserve">Laceración</t>
+          <t xml:space="preserve">Fatiga muscular</t>
         </is>
       </c>
       <c r="G9" s="56" t="inlineStr">
         <is>
-          <t xml:space="preserve">Control</t>
+          <t xml:space="preserve">Influencia</t>
         </is>
       </c>
       <c r="H9" s="57" t="inlineStr">
         <is>
+          <t xml:space="preserve">2</t>
+        </is>
+      </c>
+      <c r="I9" s="57" t="inlineStr">
+        <is>
           <t xml:space="preserve">3</t>
-        </is>
-      </c>
-      <c r="I9" s="57" t="inlineStr">
-        <is>
-          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="J9" s="51">
@@ -6736,17 +6743,24 @@
       </c>
       <c r="K9" s="107" t="inlineStr">
         <is>
-          <t xml:space="preserve">sensores</t>
+          <t xml:space="preserve">ergonomía</t>
         </is>
       </c>
       <c r="L9" s="58" t="inlineStr">
         <is>
-          <t xml:space="preserve">No se requiere EPP adicional; el control es por cortinas de seguridad en el área central.</t>
+          <t xml:space="preserve">Bata/gorro de cuarto limpio (cleanroom), guantes de nitrilo, lentes de seguridad y calzado antiestático (ESD), conforme al ingreso a Cuarto Limpio ISO 7.</t>
         </is>
       </c>
       <c r="M9" s="58" t="inlineStr">
         <is>
-          <t xml:space="preserve">SOP Operación Estaciones GECKO</t>
+          <t xml:space="preserve">16-AT40-3318-00013
+16-AT40-3318-00014
+16-AT40-3318-00015
+16-AT40-3318-00016
+16-AT40-3318-00017
+16-AT40-3318-00018
+16-AT40-3318-00019
+16-AT40-3318-00020</t>
         </is>
       </c>
       <c r="N9" s="57" t="inlineStr">
@@ -6756,7 +6770,7 @@
       </c>
       <c r="O9" s="49" t="inlineStr">
         <is>
-          <t xml:space="preserve">3</t>
+          <t xml:space="preserve">4</t>
         </is>
       </c>
       <c r="P9" s="61">
@@ -6778,12 +6792,12 @@
       </c>
       <c r="B10" s="55" t="inlineStr">
         <is>
-          <t xml:space="preserve">Operación normal - movimiento/rotación del cabezal de torque</t>
+          <t xml:space="preserve">Verificación Poka Yoke de presencia/orientación de la pieza</t>
         </is>
       </c>
       <c r="C10" s="56" t="inlineStr">
         <is>
-          <t xml:space="preserve">El cabezal de torque se mueve a la posición del feeder, recoge el tornillo y se mueve a la posición de atornillado</t>
+          <t xml:space="preserve">El sensor/pin Poka Yoke de la fixtura verifica que la pieza esté correctamente orientada antes de permitir el ciclo; el operador puede tener contacto accidental con el mecanismo al cargar la pieza</t>
         </is>
       </c>
       <c r="D10" s="56" t="inlineStr">
@@ -6798,7 +6812,7 @@
       </c>
       <c r="F10" s="49" t="inlineStr">
         <is>
-          <t xml:space="preserve">Fractura</t>
+          <t xml:space="preserve">Laceración</t>
         </is>
       </c>
       <c r="G10" s="56" t="inlineStr">
@@ -6808,12 +6822,12 @@
       </c>
       <c r="H10" s="57" t="inlineStr">
         <is>
-          <t xml:space="preserve">3</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="I10" s="57" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="J10" s="51">
@@ -6822,17 +6836,24 @@
       </c>
       <c r="K10" s="107" t="inlineStr">
         <is>
-          <t xml:space="preserve">sensores</t>
+          <t xml:space="preserve">Resguardos mecánicos</t>
         </is>
       </c>
       <c r="L10" s="58" t="inlineStr">
         <is>
-          <t xml:space="preserve">No se requiere EPP adicional; el control es por cortinas de seguridad en el área central (mismo set que protege gantry y slider).</t>
+          <t xml:space="preserve">Bata/gorro de cuarto limpio (cleanroom), guantes de nitrilo, lentes de seguridad y calzado antiestático (ESD), conforme al ingreso a Cuarto Limpio ISO 7.</t>
         </is>
       </c>
       <c r="M10" s="58" t="inlineStr">
         <is>
-          <t xml:space="preserve">SOP Operación Estaciones GECKO</t>
+          <t xml:space="preserve">16-AT40-3318-00013
+16-AT40-3318-00014
+16-AT40-3318-00015
+16-AT40-3318-00016
+16-AT40-3318-00017
+16-AT40-3318-00018
+16-AT40-3318-00019
+16-AT40-3318-00020</t>
         </is>
       </c>
       <c r="N10" s="57" t="inlineStr">
@@ -6859,17 +6880,17 @@
     <row r="11" spans="1:19" s="19" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A11" s="55" t="inlineStr">
         <is>
-          <t xml:space="preserve">No rutinario</t>
+          <t xml:space="preserve">Rutinario</t>
         </is>
       </c>
       <c r="B11" s="55" t="inlineStr">
         <is>
-          <t xml:space="preserve">Mantenimiento - cambio de motor, eje o cable</t>
+          <t xml:space="preserve">Lectura de código con escáner fijo</t>
         </is>
       </c>
       <c r="C11" s="56" t="inlineStr">
         <is>
-          <t xml:space="preserve">El personal de mantenimiento cambia el switch de llave a modo mantenimiento y bloquea el switch general de energía antes de intervenir</t>
+          <t xml:space="preserve">El escáner fijo lee el código de la pieza/etiqueta antes o durante el ciclo; el operador puede golpearse con el escáner o golpear material al cargar/descargar</t>
         </is>
       </c>
       <c r="D11" s="56" t="inlineStr">
@@ -6884,7 +6905,7 @@
       </c>
       <c r="F11" s="49" t="inlineStr">
         <is>
-          <t xml:space="preserve">Atrapamiento</t>
+          <t xml:space="preserve">Laceración</t>
         </is>
       </c>
       <c r="G11" s="56" t="inlineStr">
@@ -6894,12 +6915,12 @@
       </c>
       <c r="H11" s="57" t="inlineStr">
         <is>
-          <t xml:space="preserve">5</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="I11" s="57" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="J11" s="51">
@@ -6908,17 +6929,24 @@
       </c>
       <c r="K11" s="107" t="inlineStr">
         <is>
-          <t xml:space="preserve">LOTO</t>
+          <t xml:space="preserve">Resguardos mecánicos</t>
         </is>
       </c>
       <c r="L11" s="58" t="inlineStr">
         <is>
-          <t xml:space="preserve">No se requiere EPP adicional; candado y tarjeta de bloqueo en el switch general.</t>
+          <t xml:space="preserve">Bata/gorro de cuarto limpio (cleanroom), guantes de nitrilo, lentes de seguridad y calzado antiestático (ESD), conforme al ingreso a Cuarto Limpio ISO 7.</t>
         </is>
       </c>
       <c r="M11" s="58" t="inlineStr">
         <is>
-          <t xml:space="preserve">Procedimiento LOTO de la estación</t>
+          <t xml:space="preserve">16-AT40-3318-00013
+16-AT40-3318-00014
+16-AT40-3318-00015
+16-AT40-3318-00016
+16-AT40-3318-00017
+16-AT40-3318-00018
+16-AT40-3318-00019
+16-AT40-3318-00020</t>
         </is>
       </c>
       <c r="N11" s="57" t="inlineStr">
@@ -6950,12 +6978,12 @@
       </c>
       <c r="B12" s="55" t="inlineStr">
         <is>
-          <t xml:space="preserve">Operación normal - recolección de tornillo por succión de vacío en el feeder</t>
+          <t xml:space="preserve">Contacto con partes fijas de la fixtura (bordes/topes)</t>
         </is>
       </c>
       <c r="C12" s="56" t="inlineStr">
         <is>
-          <t xml:space="preserve">La electroválvula de vacío recoge el tornillo del feeder antes de llevarlo a la posición de atornillado</t>
+          <t xml:space="preserve">El operador puede golpearse o atraparse los dedos con los bordes/topes fijos de la fixtura al colocar o retirar la pieza</t>
         </is>
       </c>
       <c r="D12" s="56" t="inlineStr">
@@ -6980,7 +7008,7 @@
       </c>
       <c r="H12" s="57" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="I12" s="57" t="inlineStr">
@@ -6999,12 +7027,19 @@
       </c>
       <c r="L12" s="58" t="inlineStr">
         <is>
-          <t xml:space="preserve">No se requiere EPP adicional; guarda fija en el punto de recolección del feeder.</t>
+          <t xml:space="preserve">Bata/gorro de cuarto limpio (cleanroom), guantes de nitrilo, lentes de seguridad y calzado antiestático (ESD), conforme al ingreso a Cuarto Limpio ISO 7.</t>
         </is>
       </c>
       <c r="M12" s="58" t="inlineStr">
         <is>
-          <t xml:space="preserve">SOP Operación Estaciones GECKO</t>
+          <t xml:space="preserve">16-AT40-3318-00013
+16-AT40-3318-00014
+16-AT40-3318-00015
+16-AT40-3318-00016
+16-AT40-3318-00017
+16-AT40-3318-00018
+16-AT40-3318-00019
+16-AT40-3318-00020</t>
         </is>
       </c>
       <c r="N12" s="57" t="inlineStr">
@@ -7031,32 +7066,32 @@
     <row r="13" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A13" s="55" t="inlineStr">
         <is>
-          <t xml:space="preserve">No rutinario</t>
+          <t xml:space="preserve">Rutinario</t>
         </is>
       </c>
       <c r="B13" s="55" t="inlineStr">
         <is>
-          <t xml:space="preserve">Mantenimiento correctivo / solución de problemas eléctricos</t>
+          <t xml:space="preserve">Ciclo automático de atornillado (gantry, slider, cabezal de torque)</t>
         </is>
       </c>
       <c r="C13" s="56" t="inlineStr">
         <is>
-          <t xml:space="preserve">El personal de mantenimiento abre el gabinete/panel eléctrico de la estación para diagnóstico o reparación</t>
+          <t xml:space="preserve">Paso 1 de 3: el slider mueve la fixtura con la pieza clampeada hacia la posición de atornillado durante el ciclo automático; las cortinas de seguridad del área central impiden el acceso durante este movimiento</t>
         </is>
       </c>
       <c r="D13" s="56" t="inlineStr">
         <is>
-          <t xml:space="preserve">Eléctrico</t>
+          <t xml:space="preserve">Mecanico</t>
         </is>
       </c>
       <c r="E13" s="49" t="inlineStr">
         <is>
-          <t xml:space="preserve">Conductores energizados</t>
+          <t xml:space="preserve">Partes móviles</t>
         </is>
       </c>
       <c r="F13" s="49" t="inlineStr">
         <is>
-          <t xml:space="preserve">Electrocución</t>
+          <t xml:space="preserve">Laceración</t>
         </is>
       </c>
       <c r="G13" s="56" t="inlineStr">
@@ -7066,7 +7101,7 @@
       </c>
       <c r="H13" s="57" t="inlineStr">
         <is>
-          <t xml:space="preserve">5</t>
+          <t xml:space="preserve">3</t>
         </is>
       </c>
       <c r="I13" s="57" t="inlineStr">
@@ -7080,17 +7115,24 @@
       </c>
       <c r="K13" s="107" t="inlineStr">
         <is>
-          <t xml:space="preserve">LOTO</t>
+          <t xml:space="preserve">sensores</t>
         </is>
       </c>
       <c r="L13" s="58" t="inlineStr">
         <is>
-          <t xml:space="preserve">Guantes dieléctricos (clase según voltaje) y calzado aislante.</t>
+          <t xml:space="preserve">Bata/gorro de cuarto limpio (cleanroom), guantes de nitrilo, lentes de seguridad y calzado antiestático (ESD), conforme al ingreso a Cuarto Limpio ISO 7.</t>
         </is>
       </c>
       <c r="M13" s="58" t="inlineStr">
         <is>
-          <t xml:space="preserve">Procedimiento LOTO de la estación</t>
+          <t xml:space="preserve">16-AT40-3318-00013
+16-AT40-3318-00014
+16-AT40-3318-00015
+16-AT40-3318-00016
+16-AT40-3318-00017
+16-AT40-3318-00018
+16-AT40-3318-00019
+16-AT40-3318-00020</t>
         </is>
       </c>
       <c r="N13" s="57" t="inlineStr">
@@ -7100,7 +7142,7 @@
       </c>
       <c r="O13" s="49" t="inlineStr">
         <is>
-          <t xml:space="preserve">4</t>
+          <t xml:space="preserve">3</t>
         </is>
       </c>
       <c r="P13" s="61">
@@ -7122,42 +7164,42 @@
       </c>
       <c r="B14" s="55" t="inlineStr">
         <is>
-          <t xml:space="preserve">Manejo de materiales - clampeo manual de la pieza</t>
+          <t xml:space="preserve">Ciclo automático de atornillado (gantry, slider, cabezal de torque)</t>
         </is>
       </c>
       <c r="C14" s="56" t="inlineStr">
         <is>
-          <t xml:space="preserve">El operador coloca la pieza en la fixtura y cierra los 2 clamps manuales cada ciclo</t>
+          <t xml:space="preserve">Paso 2 de 3: el cabezal de torque se mueve a la posición del feeder, recoge el tornillo por succión de vacío y se mueve a la posición de atornillado</t>
         </is>
       </c>
       <c r="D14" s="56" t="inlineStr">
         <is>
-          <t xml:space="preserve">Ergonomía</t>
+          <t xml:space="preserve">Mecanico</t>
         </is>
       </c>
       <c r="E14" s="49" t="inlineStr">
         <is>
-          <t xml:space="preserve">Movimientos repetitivos</t>
+          <t xml:space="preserve">Partes móviles</t>
         </is>
       </c>
       <c r="F14" s="49" t="inlineStr">
         <is>
-          <t xml:space="preserve">Fatiga muscular</t>
+          <t xml:space="preserve">Fractura</t>
         </is>
       </c>
       <c r="G14" s="56" t="inlineStr">
         <is>
-          <t xml:space="preserve">Influencia</t>
+          <t xml:space="preserve">Control</t>
         </is>
       </c>
       <c r="H14" s="57" t="inlineStr">
         <is>
+          <t xml:space="preserve">3</t>
+        </is>
+      </c>
+      <c r="I14" s="57" t="inlineStr">
+        <is>
           <t xml:space="preserve">2</t>
-        </is>
-      </c>
-      <c r="I14" s="57" t="inlineStr">
-        <is>
-          <t xml:space="preserve">3</t>
         </is>
       </c>
       <c r="J14" s="51">
@@ -7166,17 +7208,24 @@
       </c>
       <c r="K14" s="107" t="inlineStr">
         <is>
-          <t xml:space="preserve">ergonomía</t>
+          <t xml:space="preserve">sensores</t>
         </is>
       </c>
       <c r="L14" s="58" t="inlineStr">
         <is>
-          <t xml:space="preserve">No se requiere EPP adicional.</t>
+          <t xml:space="preserve">Bata/gorro de cuarto limpio (cleanroom), guantes de nitrilo, lentes de seguridad y calzado antiestático (ESD), conforme al ingreso a Cuarto Limpio ISO 7.</t>
         </is>
       </c>
       <c r="M14" s="58" t="inlineStr">
         <is>
-          <t xml:space="preserve">Evaluación ergonómica de la estación</t>
+          <t xml:space="preserve">16-AT40-3318-00013
+16-AT40-3318-00014
+16-AT40-3318-00015
+16-AT40-3318-00016
+16-AT40-3318-00017
+16-AT40-3318-00018
+16-AT40-3318-00019
+16-AT40-3318-00020</t>
         </is>
       </c>
       <c r="N14" s="57" t="inlineStr">
@@ -7186,7 +7235,7 @@
       </c>
       <c r="O14" s="49" t="inlineStr">
         <is>
-          <t xml:space="preserve">4</t>
+          <t xml:space="preserve">3</t>
         </is>
       </c>
       <c r="P14" s="61">
@@ -7203,17 +7252,17 @@
     <row r="15" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A15" s="55" t="inlineStr">
         <is>
-          <t xml:space="preserve">No rutinario</t>
+          <t xml:space="preserve">Rutinario</t>
         </is>
       </c>
       <c r="B15" s="55" t="inlineStr">
         <is>
-          <t xml:space="preserve">Mantenimiento - energía neumática residual del sistema de vacío</t>
+          <t xml:space="preserve">Ciclo automático de atornillado (gantry, slider, cabezal de torque)</t>
         </is>
       </c>
       <c r="C15" s="56" t="inlineStr">
         <is>
-          <t xml:space="preserve">El personal de mantenimiento interviene la línea neumática de la electroválvula de vacío; actualmente no existe válvula de despresurización/bloqueo LOTO neumático (en proceso de compra)</t>
+          <t xml:space="preserve">Paso 3 de 3: el slider regresa la pieza a la posición frontal para que el operador la descargue</t>
         </is>
       </c>
       <c r="D15" s="56" t="inlineStr">
@@ -7223,22 +7272,22 @@
       </c>
       <c r="E15" s="49" t="inlineStr">
         <is>
-          <t xml:space="preserve">Sistema de presión</t>
+          <t xml:space="preserve">Partes móviles</t>
         </is>
       </c>
       <c r="F15" s="49" t="inlineStr">
         <is>
-          <t xml:space="preserve">Laceraciones</t>
+          <t xml:space="preserve">Laceración</t>
         </is>
       </c>
       <c r="G15" s="56" t="inlineStr">
         <is>
-          <t xml:space="preserve">Influencia</t>
+          <t xml:space="preserve">Control</t>
         </is>
       </c>
       <c r="H15" s="57" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="I15" s="57" t="inlineStr">
@@ -7252,17 +7301,24 @@
       </c>
       <c r="K15" s="107" t="inlineStr">
         <is>
-          <t xml:space="preserve">inspecciones periódicas</t>
+          <t xml:space="preserve">Resguardos mecánicos</t>
         </is>
       </c>
       <c r="L15" s="58" t="inlineStr">
         <is>
-          <t xml:space="preserve">No se requiere EPP adicional. Riesgo bajo: solo succión de baja presión, sin pistones. Pendiente instalar válvula de despresurización/bloqueo LOTO neumático (en compra); mientras tanto solo se cuenta con inspección periódica del circuito.</t>
+          <t xml:space="preserve">Bata/gorro de cuarto limpio (cleanroom), guantes de nitrilo, lentes de seguridad y calzado antiestático (ESD), conforme al ingreso a Cuarto Limpio ISO 7.</t>
         </is>
       </c>
       <c r="M15" s="58" t="inlineStr">
         <is>
-          <t xml:space="preserve">Procedimiento LOTO de la estación (pendiente actualizar con válvula neumática)</t>
+          <t xml:space="preserve">16-AT40-3318-00013
+16-AT40-3318-00014
+16-AT40-3318-00015
+16-AT40-3318-00016
+16-AT40-3318-00017
+16-AT40-3318-00018
+16-AT40-3318-00019
+16-AT40-3318-00020</t>
         </is>
       </c>
       <c r="N15" s="57" t="inlineStr">
@@ -7272,7 +7328,7 @@
       </c>
       <c r="O15" s="49" t="inlineStr">
         <is>
-          <t xml:space="preserve">5</t>
+          <t xml:space="preserve">3</t>
         </is>
       </c>
       <c r="P15" s="61">
@@ -7287,24 +7343,87 @@
       <c r="S15" s="57"/>
     </row>
     <row r="16" spans="1:19" x14ac:dyDescent="0.2">
-      <c r="A16" s="55"/>
-      <c r="B16" s="55"/>
-      <c r="C16" s="56"/>
-      <c r="D16" s="56"/>
-      <c r="E16" s="49"/>
-      <c r="F16" s="49"/>
-      <c r="G16" s="56"/>
-      <c r="H16" s="57"/>
-      <c r="I16" s="57"/>
+      <c r="A16" s="55" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Rutinario</t>
+        </is>
+      </c>
+      <c r="B16" s="55" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Descarga de la pieza terminada</t>
+        </is>
+      </c>
+      <c r="C16" s="56" t="inlineStr">
+        <is>
+          <t xml:space="preserve">El operador retira la pieza terminada de la fixtura y la coloca en el contenedor de salida</t>
+        </is>
+      </c>
+      <c r="D16" s="56" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Ergonomía</t>
+        </is>
+      </c>
+      <c r="E16" s="49" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Movimientos repetitivos</t>
+        </is>
+      </c>
+      <c r="F16" s="49" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Fatiga muscular</t>
+        </is>
+      </c>
+      <c r="G16" s="56" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Influencia</t>
+        </is>
+      </c>
+      <c r="H16" s="57" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2</t>
+        </is>
+      </c>
+      <c r="I16" s="57" t="inlineStr">
+        <is>
+          <t xml:space="preserve">3</t>
+        </is>
+      </c>
       <c r="J16" s="51">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="K16" s="107"/>
-      <c r="L16" s="58"/>
-      <c r="M16" s="58"/>
-      <c r="N16" s="57"/>
-      <c r="O16" s="49"/>
+      <c r="K16" s="107" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ergonomía</t>
+        </is>
+      </c>
+      <c r="L16" s="58" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Bata/gorro de cuarto limpio (cleanroom), guantes de nitrilo, lentes de seguridad y calzado antiestático (ESD), conforme al ingreso a Cuarto Limpio ISO 7.</t>
+        </is>
+      </c>
+      <c r="M16" s="58" t="inlineStr">
+        <is>
+          <t xml:space="preserve">16-AT40-3318-00013
+16-AT40-3318-00014
+16-AT40-3318-00015
+16-AT40-3318-00016
+16-AT40-3318-00017
+16-AT40-3318-00018
+16-AT40-3318-00019
+16-AT40-3318-00020</t>
+        </is>
+      </c>
+      <c r="N16" s="57" t="inlineStr">
+        <is>
+          <t xml:space="preserve">EHS / Automation</t>
+        </is>
+      </c>
+      <c r="O16" s="49" t="inlineStr">
+        <is>
+          <t xml:space="preserve">4</t>
+        </is>
+      </c>
       <c r="P16" s="61">
         <f t="shared" si="4"/>
         <v>0</v>
@@ -7317,24 +7436,87 @@
       <c r="S16" s="57"/>
     </row>
     <row r="17" spans="1:19" x14ac:dyDescent="0.2">
-      <c r="A17" s="55"/>
-      <c r="B17" s="55"/>
-      <c r="C17" s="56"/>
-      <c r="D17" s="56"/>
-      <c r="E17" s="49"/>
-      <c r="F17" s="49"/>
-      <c r="G17" s="56"/>
-      <c r="H17" s="57"/>
-      <c r="I17" s="57"/>
+      <c r="A17" s="55" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Rutinario</t>
+        </is>
+      </c>
+      <c r="B17" s="55" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Islas de conexión eléctrica (alimentación y sensores)</t>
+        </is>
+      </c>
+      <c r="C17" s="56" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Las islas/bloques de conexión eléctrica de alimentación y de sensores quedan accesibles en el área de trabajo durante la operación normal</t>
+        </is>
+      </c>
+      <c r="D17" s="56" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Eléctrico</t>
+        </is>
+      </c>
+      <c r="E17" s="49" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Conductores energizados</t>
+        </is>
+      </c>
+      <c r="F17" s="49" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Electrocución</t>
+        </is>
+      </c>
+      <c r="G17" s="56" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Control</t>
+        </is>
+      </c>
+      <c r="H17" s="57" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2</t>
+        </is>
+      </c>
+      <c r="I17" s="57" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1</t>
+        </is>
+      </c>
       <c r="J17" s="51">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="K17" s="107"/>
-      <c r="L17" s="58"/>
-      <c r="M17" s="58"/>
-      <c r="N17" s="57"/>
-      <c r="O17" s="49"/>
+      <c r="K17" s="107" t="inlineStr">
+        <is>
+          <t xml:space="preserve">detección de voltaje</t>
+        </is>
+      </c>
+      <c r="L17" s="58" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Bata/gorro de cuarto limpio (cleanroom), guantes de nitrilo, lentes de seguridad y calzado antiestático (ESD), conforme al ingreso a Cuarto Limpio ISO 7. Adicional para intervención eléctrica: guantes dieléctricos (clase según voltaje) y calzado aislante.</t>
+        </is>
+      </c>
+      <c r="M17" s="58" t="inlineStr">
+        <is>
+          <t xml:space="preserve">16-AT40-3318-00013
+16-AT40-3318-00014
+16-AT40-3318-00015
+16-AT40-3318-00016
+16-AT40-3318-00017
+16-AT40-3318-00018
+16-AT40-3318-00019
+16-AT40-3318-00020</t>
+        </is>
+      </c>
+      <c r="N17" s="57" t="inlineStr">
+        <is>
+          <t xml:space="preserve">EHS / Automation</t>
+        </is>
+      </c>
+      <c r="O17" s="49" t="inlineStr">
+        <is>
+          <t xml:space="preserve">3</t>
+        </is>
+      </c>
       <c r="P17" s="61">
         <f t="shared" si="4"/>
         <v>0</v>
@@ -7347,24 +7529,87 @@
       <c r="S17" s="57"/>
     </row>
     <row r="18" spans="1:19" x14ac:dyDescent="0.2">
-      <c r="A18" s="55"/>
-      <c r="B18" s="55"/>
-      <c r="C18" s="56"/>
-      <c r="D18" s="56"/>
-      <c r="E18" s="49"/>
-      <c r="F18" s="49"/>
-      <c r="G18" s="56"/>
-      <c r="H18" s="57"/>
-      <c r="I18" s="57"/>
+      <c r="A18" s="55" t="inlineStr">
+        <is>
+          <t xml:space="preserve">No rutinario</t>
+        </is>
+      </c>
+      <c r="B18" s="55" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Arranque de la estación al inicio de turno</t>
+        </is>
+      </c>
+      <c r="C18" s="56" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Paso 1 de 2: energiza el switch general y coloca el switch de llave en modo Automático</t>
+        </is>
+      </c>
+      <c r="D18" s="56" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Eléctrico</t>
+        </is>
+      </c>
+      <c r="E18" s="49" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Conductores energizados</t>
+        </is>
+      </c>
+      <c r="F18" s="49" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Electrocución</t>
+        </is>
+      </c>
+      <c r="G18" s="56" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Control</t>
+        </is>
+      </c>
+      <c r="H18" s="57" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2</t>
+        </is>
+      </c>
+      <c r="I18" s="57" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1</t>
+        </is>
+      </c>
       <c r="J18" s="51">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="K18" s="107"/>
-      <c r="L18" s="58"/>
-      <c r="M18" s="58"/>
-      <c r="N18" s="57"/>
-      <c r="O18" s="49"/>
+      <c r="K18" s="107" t="inlineStr">
+        <is>
+          <t xml:space="preserve">LOTO</t>
+        </is>
+      </c>
+      <c r="L18" s="58" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Bata/gorro de cuarto limpio (cleanroom), guantes de nitrilo, lentes de seguridad y calzado antiestático (ESD), conforme al ingreso a Cuarto Limpio ISO 7. Adicional para intervención eléctrica: guantes dieléctricos (clase según voltaje) y calzado aislante.</t>
+        </is>
+      </c>
+      <c r="M18" s="58" t="inlineStr">
+        <is>
+          <t xml:space="preserve">16-AT40-3318-00013
+16-AT40-3318-00014
+16-AT40-3318-00015
+16-AT40-3318-00016
+16-AT40-3318-00017
+16-AT40-3318-00018
+16-AT40-3318-00019
+16-AT40-3318-00020</t>
+        </is>
+      </c>
+      <c r="N18" s="57" t="inlineStr">
+        <is>
+          <t xml:space="preserve">EHS / Automation</t>
+        </is>
+      </c>
+      <c r="O18" s="49" t="inlineStr">
+        <is>
+          <t xml:space="preserve">3</t>
+        </is>
+      </c>
       <c r="P18" s="61">
         <f t="shared" si="4"/>
         <v>0</v>
@@ -7377,24 +7622,87 @@
       <c r="S18" s="57"/>
     </row>
     <row r="19" spans="1:19" x14ac:dyDescent="0.2">
-      <c r="A19" s="55"/>
-      <c r="B19" s="55"/>
-      <c r="C19" s="56"/>
-      <c r="D19" s="56"/>
-      <c r="E19" s="49"/>
-      <c r="F19" s="49"/>
-      <c r="G19" s="56"/>
-      <c r="H19" s="57"/>
-      <c r="I19" s="57"/>
+      <c r="A19" s="55" t="inlineStr">
+        <is>
+          <t xml:space="preserve">No rutinario</t>
+        </is>
+      </c>
+      <c r="B19" s="55" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Arranque de la estación al inicio de turno</t>
+        </is>
+      </c>
+      <c r="C19" s="56" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Paso 2 de 2: inicializa el gantry (homing) y verifica que las cortinas de seguridad y el botón de reset funcionen correctamente antes de operar</t>
+        </is>
+      </c>
+      <c r="D19" s="56" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Mecanico</t>
+        </is>
+      </c>
+      <c r="E19" s="49" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Partes móviles</t>
+        </is>
+      </c>
+      <c r="F19" s="49" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Atrapamiento</t>
+        </is>
+      </c>
+      <c r="G19" s="56" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Control</t>
+        </is>
+      </c>
+      <c r="H19" s="57" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2</t>
+        </is>
+      </c>
+      <c r="I19" s="57" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1</t>
+        </is>
+      </c>
       <c r="J19" s="51">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="K19" s="107"/>
-      <c r="L19" s="58"/>
-      <c r="M19" s="58"/>
-      <c r="N19" s="57"/>
-      <c r="O19" s="49"/>
+      <c r="K19" s="107" t="inlineStr">
+        <is>
+          <t xml:space="preserve">sensores</t>
+        </is>
+      </c>
+      <c r="L19" s="58" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Bata/gorro de cuarto limpio (cleanroom), guantes de nitrilo, lentes de seguridad y calzado antiestático (ESD), conforme al ingreso a Cuarto Limpio ISO 7.</t>
+        </is>
+      </c>
+      <c r="M19" s="58" t="inlineStr">
+        <is>
+          <t xml:space="preserve">16-AT40-3318-00013
+16-AT40-3318-00014
+16-AT40-3318-00015
+16-AT40-3318-00016
+16-AT40-3318-00017
+16-AT40-3318-00018
+16-AT40-3318-00019
+16-AT40-3318-00020</t>
+        </is>
+      </c>
+      <c r="N19" s="57" t="inlineStr">
+        <is>
+          <t xml:space="preserve">EHS / Automation</t>
+        </is>
+      </c>
+      <c r="O19" s="49" t="inlineStr">
+        <is>
+          <t xml:space="preserve">3</t>
+        </is>
+      </c>
       <c r="P19" s="61">
         <f t="shared" si="4"/>
         <v>0</v>
@@ -7407,24 +7715,87 @@
       <c r="S19" s="57"/>
     </row>
     <row r="20" spans="1:19" x14ac:dyDescent="0.2">
-      <c r="A20" s="55"/>
-      <c r="B20" s="55"/>
-      <c r="C20" s="56"/>
-      <c r="D20" s="56"/>
-      <c r="E20" s="49"/>
-      <c r="F20" s="49"/>
-      <c r="G20" s="56"/>
-      <c r="H20" s="57"/>
-      <c r="I20" s="57"/>
+      <c r="A20" s="55" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Emergencia </t>
+        </is>
+      </c>
+      <c r="B20" s="55" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Activación del botón de paro de emergencia ante una condición insegura</t>
+        </is>
+      </c>
+      <c r="C20" s="56" t="inlineStr">
+        <is>
+          <t xml:space="preserve">El operador presiona el botón de paro de emergencia al detectar una condición insegura (atasco de pieza, invasión del área central, ruido anormal) y notifica a su supervisor/mantenimiento</t>
+        </is>
+      </c>
+      <c r="D20" s="56" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Mecanico</t>
+        </is>
+      </c>
+      <c r="E20" s="49" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Partes móviles</t>
+        </is>
+      </c>
+      <c r="F20" s="49" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Atrapamiento</t>
+        </is>
+      </c>
+      <c r="G20" s="56" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Control</t>
+        </is>
+      </c>
+      <c r="H20" s="57" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1</t>
+        </is>
+      </c>
+      <c r="I20" s="57" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1</t>
+        </is>
+      </c>
       <c r="J20" s="51">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="K20" s="107"/>
-      <c r="L20" s="58"/>
-      <c r="M20" s="58"/>
-      <c r="N20" s="57"/>
-      <c r="O20" s="49"/>
+      <c r="K20" s="107" t="inlineStr">
+        <is>
+          <t xml:space="preserve">sensores</t>
+        </is>
+      </c>
+      <c r="L20" s="58" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Bata/gorro de cuarto limpio (cleanroom), guantes de nitrilo, lentes de seguridad y calzado antiestático (ESD), conforme al ingreso a Cuarto Limpio ISO 7.</t>
+        </is>
+      </c>
+      <c r="M20" s="58" t="inlineStr">
+        <is>
+          <t xml:space="preserve">16-AT40-3318-00013
+16-AT40-3318-00014
+16-AT40-3318-00015
+16-AT40-3318-00016
+16-AT40-3318-00017
+16-AT40-3318-00018
+16-AT40-3318-00019
+16-AT40-3318-00020</t>
+        </is>
+      </c>
+      <c r="N20" s="57" t="inlineStr">
+        <is>
+          <t xml:space="preserve">EHS / Automation</t>
+        </is>
+      </c>
+      <c r="O20" s="49" t="inlineStr">
+        <is>
+          <t xml:space="preserve">3</t>
+        </is>
+      </c>
       <c r="P20" s="61">
         <f t="shared" si="4"/>
         <v>0</v>
@@ -7437,24 +7808,87 @@
       <c r="S20" s="57"/>
     </row>
     <row r="21" spans="1:19" x14ac:dyDescent="0.2">
-      <c r="A21" s="55"/>
-      <c r="B21" s="55"/>
-      <c r="C21" s="56"/>
-      <c r="D21" s="56"/>
-      <c r="E21" s="49"/>
-      <c r="F21" s="49"/>
-      <c r="G21" s="56"/>
-      <c r="H21" s="57"/>
-      <c r="I21" s="57"/>
+      <c r="A21" s="55" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Emergencia </t>
+        </is>
+      </c>
+      <c r="B21" s="55" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Reinicio del equipo después de un paro de emergencia</t>
+        </is>
+      </c>
+      <c r="C21" s="56" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Personal autorizado identifica y corrige la causa del paro (ej. libera el atasco con el switch en modo mantenimiento), verifica que el área esté despejada antes de presionar reset y reiniciar el ciclo</t>
+        </is>
+      </c>
+      <c r="D21" s="56" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Mecanico</t>
+        </is>
+      </c>
+      <c r="E21" s="49" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Partes móviles</t>
+        </is>
+      </c>
+      <c r="F21" s="49" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Atrapamiento</t>
+        </is>
+      </c>
+      <c r="G21" s="56" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Control</t>
+        </is>
+      </c>
+      <c r="H21" s="57" t="inlineStr">
+        <is>
+          <t xml:space="preserve">3</t>
+        </is>
+      </c>
+      <c r="I21" s="57" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1</t>
+        </is>
+      </c>
       <c r="J21" s="51">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="K21" s="107"/>
-      <c r="L21" s="58"/>
-      <c r="M21" s="58"/>
-      <c r="N21" s="57"/>
-      <c r="O21" s="49"/>
+      <c r="K21" s="107" t="inlineStr">
+        <is>
+          <t xml:space="preserve">LOTO</t>
+        </is>
+      </c>
+      <c r="L21" s="58" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Bata/gorro de cuarto limpio (cleanroom), guantes de nitrilo, lentes de seguridad y calzado antiestático (ESD), conforme al ingreso a Cuarto Limpio ISO 7.</t>
+        </is>
+      </c>
+      <c r="M21" s="58" t="inlineStr">
+        <is>
+          <t xml:space="preserve">16-AT40-3318-00013
+16-AT40-3318-00014
+16-AT40-3318-00015
+16-AT40-3318-00016
+16-AT40-3318-00017
+16-AT40-3318-00018
+16-AT40-3318-00019
+16-AT40-3318-00020</t>
+        </is>
+      </c>
+      <c r="N21" s="57" t="inlineStr">
+        <is>
+          <t xml:space="preserve">EHS / Automation</t>
+        </is>
+      </c>
+      <c r="O21" s="49" t="inlineStr">
+        <is>
+          <t xml:space="preserve">3</t>
+        </is>
+      </c>
       <c r="P21" s="61">
         <f t="shared" si="4"/>
         <v>0</v>
@@ -7467,24 +7901,87 @@
       <c r="S21" s="57"/>
     </row>
     <row r="22" spans="1:19" x14ac:dyDescent="0.2">
-      <c r="A22" s="55"/>
-      <c r="B22" s="55"/>
-      <c r="C22" s="56"/>
-      <c r="D22" s="56"/>
-      <c r="E22" s="49"/>
-      <c r="F22" s="49"/>
-      <c r="G22" s="56"/>
-      <c r="H22" s="57"/>
-      <c r="I22" s="57"/>
+      <c r="A22" s="55" t="inlineStr">
+        <is>
+          <t xml:space="preserve">No rutinario</t>
+        </is>
+      </c>
+      <c r="B22" s="55" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Mantenimiento mecánico - cambio de motor, eje o cable</t>
+        </is>
+      </c>
+      <c r="C22" s="56" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Paso 1 de 3: cambia el switch de llave a modo Mantenimiento y bloquea/etiqueta el switch general de energía (LOTO) antes de intervenir</t>
+        </is>
+      </c>
+      <c r="D22" s="56" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Mecanico</t>
+        </is>
+      </c>
+      <c r="E22" s="49" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Partes móviles</t>
+        </is>
+      </c>
+      <c r="F22" s="49" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Atrapamiento</t>
+        </is>
+      </c>
+      <c r="G22" s="56" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Control</t>
+        </is>
+      </c>
+      <c r="H22" s="57" t="inlineStr">
+        <is>
+          <t xml:space="preserve">5</t>
+        </is>
+      </c>
+      <c r="I22" s="57" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2</t>
+        </is>
+      </c>
       <c r="J22" s="51">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="K22" s="107"/>
-      <c r="L22" s="58"/>
-      <c r="M22" s="58"/>
-      <c r="N22" s="57"/>
-      <c r="O22" s="49"/>
+      <c r="K22" s="107" t="inlineStr">
+        <is>
+          <t xml:space="preserve">LOTO</t>
+        </is>
+      </c>
+      <c r="L22" s="58" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Bata/gorro de cuarto limpio (cleanroom), guantes de nitrilo, lentes de seguridad y calzado antiestático (ESD), conforme al ingreso a Cuarto Limpio ISO 7. Adicional para intervención eléctrica: guantes dieléctricos (clase según voltaje) y calzado aislante.</t>
+        </is>
+      </c>
+      <c r="M22" s="58" t="inlineStr">
+        <is>
+          <t xml:space="preserve">16-AT40-3318-00013
+16-AT40-3318-00014
+16-AT40-3318-00015
+16-AT40-3318-00016
+16-AT40-3318-00017
+16-AT40-3318-00018
+16-AT40-3318-00019
+16-AT40-3318-00020</t>
+        </is>
+      </c>
+      <c r="N22" s="57" t="inlineStr">
+        <is>
+          <t xml:space="preserve">EHS / Automation</t>
+        </is>
+      </c>
+      <c r="O22" s="49" t="inlineStr">
+        <is>
+          <t xml:space="preserve">3</t>
+        </is>
+      </c>
       <c r="P22" s="61">
         <f t="shared" si="4"/>
         <v>0</v>
@@ -7497,24 +7994,87 @@
       <c r="S22" s="57"/>
     </row>
     <row r="23" spans="1:19" x14ac:dyDescent="0.2">
-      <c r="A23" s="55"/>
-      <c r="B23" s="55"/>
-      <c r="C23" s="56"/>
-      <c r="D23" s="56"/>
-      <c r="E23" s="49"/>
-      <c r="F23" s="49"/>
-      <c r="G23" s="56"/>
-      <c r="H23" s="57"/>
-      <c r="I23" s="57"/>
+      <c r="A23" s="55" t="inlineStr">
+        <is>
+          <t xml:space="preserve">No rutinario</t>
+        </is>
+      </c>
+      <c r="B23" s="55" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Mantenimiento mecánico - cambio de motor, eje o cable</t>
+        </is>
+      </c>
+      <c r="C23" s="56" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Paso 2 de 3: reemplaza el componente (motor, eje o cable) del gantry/slider/cabezal de torque</t>
+        </is>
+      </c>
+      <c r="D23" s="56" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Mecanico</t>
+        </is>
+      </c>
+      <c r="E23" s="49" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Partes móviles</t>
+        </is>
+      </c>
+      <c r="F23" s="49" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Atrapamiento</t>
+        </is>
+      </c>
+      <c r="G23" s="56" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Control</t>
+        </is>
+      </c>
+      <c r="H23" s="57" t="inlineStr">
+        <is>
+          <t xml:space="preserve">4</t>
+        </is>
+      </c>
+      <c r="I23" s="57" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1</t>
+        </is>
+      </c>
       <c r="J23" s="51">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="K23" s="107"/>
-      <c r="L23" s="58"/>
-      <c r="M23" s="58"/>
-      <c r="N23" s="57"/>
-      <c r="O23" s="49"/>
+      <c r="K23" s="107" t="inlineStr">
+        <is>
+          <t xml:space="preserve">LOTO</t>
+        </is>
+      </c>
+      <c r="L23" s="58" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Bata/gorro de cuarto limpio (cleanroom), guantes de nitrilo, lentes de seguridad y calzado antiestático (ESD), conforme al ingreso a Cuarto Limpio ISO 7.</t>
+        </is>
+      </c>
+      <c r="M23" s="58" t="inlineStr">
+        <is>
+          <t xml:space="preserve">16-AT40-3318-00013
+16-AT40-3318-00014
+16-AT40-3318-00015
+16-AT40-3318-00016
+16-AT40-3318-00017
+16-AT40-3318-00018
+16-AT40-3318-00019
+16-AT40-3318-00020</t>
+        </is>
+      </c>
+      <c r="N23" s="57" t="inlineStr">
+        <is>
+          <t xml:space="preserve">EHS / Automation</t>
+        </is>
+      </c>
+      <c r="O23" s="49" t="inlineStr">
+        <is>
+          <t xml:space="preserve">3</t>
+        </is>
+      </c>
       <c r="P23" s="61">
         <f t="shared" si="4"/>
         <v>0</v>
@@ -7527,24 +8087,87 @@
       <c r="S23" s="57"/>
     </row>
     <row r="24" spans="1:19" x14ac:dyDescent="0.2">
-      <c r="A24" s="55"/>
-      <c r="B24" s="55"/>
-      <c r="C24" s="56"/>
-      <c r="D24" s="56"/>
-      <c r="E24" s="49"/>
-      <c r="F24" s="49"/>
-      <c r="G24" s="56"/>
-      <c r="H24" s="57"/>
-      <c r="I24" s="57"/>
+      <c r="A24" s="55" t="inlineStr">
+        <is>
+          <t xml:space="preserve">No rutinario</t>
+        </is>
+      </c>
+      <c r="B24" s="55" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Mantenimiento mecánico - cambio de motor, eje o cable</t>
+        </is>
+      </c>
+      <c r="C24" s="56" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Paso 3 de 3: retira el bloqueo LOTO y realiza una prueba funcional del equipo con las cortinas de seguridad activas</t>
+        </is>
+      </c>
+      <c r="D24" s="56" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Mecanico</t>
+        </is>
+      </c>
+      <c r="E24" s="49" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Partes móviles</t>
+        </is>
+      </c>
+      <c r="F24" s="49" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Atrapamiento</t>
+        </is>
+      </c>
+      <c r="G24" s="56" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Control</t>
+        </is>
+      </c>
+      <c r="H24" s="57" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2</t>
+        </is>
+      </c>
+      <c r="I24" s="57" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1</t>
+        </is>
+      </c>
       <c r="J24" s="51">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="K24" s="107"/>
-      <c r="L24" s="58"/>
-      <c r="M24" s="58"/>
-      <c r="N24" s="57"/>
-      <c r="O24" s="49"/>
+      <c r="K24" s="107" t="inlineStr">
+        <is>
+          <t xml:space="preserve">sensores</t>
+        </is>
+      </c>
+      <c r="L24" s="58" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Bata/gorro de cuarto limpio (cleanroom), guantes de nitrilo, lentes de seguridad y calzado antiestático (ESD), conforme al ingreso a Cuarto Limpio ISO 7.</t>
+        </is>
+      </c>
+      <c r="M24" s="58" t="inlineStr">
+        <is>
+          <t xml:space="preserve">16-AT40-3318-00013
+16-AT40-3318-00014
+16-AT40-3318-00015
+16-AT40-3318-00016
+16-AT40-3318-00017
+16-AT40-3318-00018
+16-AT40-3318-00019
+16-AT40-3318-00020</t>
+        </is>
+      </c>
+      <c r="N24" s="57" t="inlineStr">
+        <is>
+          <t xml:space="preserve">EHS / Automation</t>
+        </is>
+      </c>
+      <c r="O24" s="49" t="inlineStr">
+        <is>
+          <t xml:space="preserve">3</t>
+        </is>
+      </c>
       <c r="P24" s="61">
         <f t="shared" si="4"/>
         <v>0</v>
@@ -7557,24 +8180,87 @@
       <c r="S24" s="57"/>
     </row>
     <row r="25" spans="1:19" x14ac:dyDescent="0.2">
-      <c r="A25" s="55"/>
-      <c r="B25" s="55"/>
-      <c r="C25" s="56"/>
-      <c r="D25" s="56"/>
-      <c r="E25" s="49"/>
-      <c r="F25" s="49"/>
-      <c r="G25" s="56"/>
-      <c r="H25" s="57"/>
-      <c r="I25" s="57"/>
+      <c r="A25" s="55" t="inlineStr">
+        <is>
+          <t xml:space="preserve">No rutinario</t>
+        </is>
+      </c>
+      <c r="B25" s="55" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Mantenimiento correctivo eléctrico</t>
+        </is>
+      </c>
+      <c r="C25" s="56" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Paso 1 de 2: bloquea y etiqueta (LOTO) el switch general y abre el gabinete/panel eléctrico de la estación para diagnóstico</t>
+        </is>
+      </c>
+      <c r="D25" s="56" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Eléctrico</t>
+        </is>
+      </c>
+      <c r="E25" s="49" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Conductores energizados</t>
+        </is>
+      </c>
+      <c r="F25" s="49" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Electrocución</t>
+        </is>
+      </c>
+      <c r="G25" s="56" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Control</t>
+        </is>
+      </c>
+      <c r="H25" s="57" t="inlineStr">
+        <is>
+          <t xml:space="preserve">5</t>
+        </is>
+      </c>
+      <c r="I25" s="57" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2</t>
+        </is>
+      </c>
       <c r="J25" s="51">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="K25" s="107"/>
-      <c r="L25" s="58"/>
-      <c r="M25" s="58"/>
-      <c r="N25" s="57"/>
-      <c r="O25" s="49"/>
+      <c r="K25" s="107" t="inlineStr">
+        <is>
+          <t xml:space="preserve">LOTO</t>
+        </is>
+      </c>
+      <c r="L25" s="58" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Bata/gorro de cuarto limpio (cleanroom), guantes de nitrilo, lentes de seguridad y calzado antiestático (ESD), conforme al ingreso a Cuarto Limpio ISO 7. Adicional para intervención eléctrica: guantes dieléctricos (clase según voltaje) y calzado aislante.</t>
+        </is>
+      </c>
+      <c r="M25" s="58" t="inlineStr">
+        <is>
+          <t xml:space="preserve">16-AT40-3318-00013
+16-AT40-3318-00014
+16-AT40-3318-00015
+16-AT40-3318-00016
+16-AT40-3318-00017
+16-AT40-3318-00018
+16-AT40-3318-00019
+16-AT40-3318-00020</t>
+        </is>
+      </c>
+      <c r="N25" s="57" t="inlineStr">
+        <is>
+          <t xml:space="preserve">EHS / Automation</t>
+        </is>
+      </c>
+      <c r="O25" s="49" t="inlineStr">
+        <is>
+          <t xml:space="preserve">3</t>
+        </is>
+      </c>
       <c r="P25" s="61">
         <f t="shared" si="4"/>
         <v>0</v>
@@ -7587,24 +8273,87 @@
       <c r="S25" s="57"/>
     </row>
     <row r="26" spans="1:19" x14ac:dyDescent="0.2">
-      <c r="A26" s="55"/>
-      <c r="B26" s="55"/>
-      <c r="C26" s="56"/>
-      <c r="D26" s="56"/>
-      <c r="E26" s="49"/>
-      <c r="F26" s="49"/>
-      <c r="G26" s="56"/>
-      <c r="H26" s="57"/>
-      <c r="I26" s="57"/>
+      <c r="A26" s="55" t="inlineStr">
+        <is>
+          <t xml:space="preserve">No rutinario</t>
+        </is>
+      </c>
+      <c r="B26" s="55" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Mantenimiento correctivo eléctrico</t>
+        </is>
+      </c>
+      <c r="C26" s="56" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Paso 2 de 2: repara o reemplaza el componente dañado, cierra el gabinete y retira el bloqueo LOTO</t>
+        </is>
+      </c>
+      <c r="D26" s="56" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Eléctrico</t>
+        </is>
+      </c>
+      <c r="E26" s="49" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Conductores energizados</t>
+        </is>
+      </c>
+      <c r="F26" s="49" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Electrocución</t>
+        </is>
+      </c>
+      <c r="G26" s="56" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Control</t>
+        </is>
+      </c>
+      <c r="H26" s="57" t="inlineStr">
+        <is>
+          <t xml:space="preserve">5</t>
+        </is>
+      </c>
+      <c r="I26" s="57" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1</t>
+        </is>
+      </c>
       <c r="J26" s="51">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="K26" s="107"/>
-      <c r="L26" s="58"/>
-      <c r="M26" s="58"/>
-      <c r="N26" s="57"/>
-      <c r="O26" s="49"/>
+      <c r="K26" s="107" t="inlineStr">
+        <is>
+          <t xml:space="preserve">LOTO</t>
+        </is>
+      </c>
+      <c r="L26" s="58" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Bata/gorro de cuarto limpio (cleanroom), guantes de nitrilo, lentes de seguridad y calzado antiestático (ESD), conforme al ingreso a Cuarto Limpio ISO 7. Adicional para intervención eléctrica: guantes dieléctricos (clase según voltaje) y calzado aislante.</t>
+        </is>
+      </c>
+      <c r="M26" s="58" t="inlineStr">
+        <is>
+          <t xml:space="preserve">16-AT40-3318-00013
+16-AT40-3318-00014
+16-AT40-3318-00015
+16-AT40-3318-00016
+16-AT40-3318-00017
+16-AT40-3318-00018
+16-AT40-3318-00019
+16-AT40-3318-00020</t>
+        </is>
+      </c>
+      <c r="N26" s="57" t="inlineStr">
+        <is>
+          <t xml:space="preserve">EHS / Automation</t>
+        </is>
+      </c>
+      <c r="O26" s="49" t="inlineStr">
+        <is>
+          <t xml:space="preserve">3</t>
+        </is>
+      </c>
       <c r="P26" s="61">
         <f t="shared" si="4"/>
         <v>0</v>
@@ -7617,24 +8366,87 @@
       <c r="S26" s="57"/>
     </row>
     <row r="27" spans="1:19" x14ac:dyDescent="0.2">
-      <c r="A27" s="55"/>
-      <c r="B27" s="55"/>
-      <c r="C27" s="56"/>
-      <c r="D27" s="56"/>
-      <c r="E27" s="49"/>
-      <c r="F27" s="49"/>
-      <c r="G27" s="56"/>
-      <c r="H27" s="57"/>
-      <c r="I27" s="57"/>
+      <c r="A27" s="55" t="inlineStr">
+        <is>
+          <t xml:space="preserve">No rutinario</t>
+        </is>
+      </c>
+      <c r="B27" s="55" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Mantenimiento - energía neumática residual del sistema de vacío</t>
+        </is>
+      </c>
+      <c r="C27" s="56" t="inlineStr">
+        <is>
+          <t xml:space="preserve">El personal de mantenimiento interviene la línea neumática de la electroválvula de vacío; actualmente no existe válvula de despresurización/bloqueo LOTO neumático dedicada (riesgo bajo: solo succión de baja presión, sin pistones)</t>
+        </is>
+      </c>
+      <c r="D27" s="56" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Mecanico</t>
+        </is>
+      </c>
+      <c r="E27" s="49" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Sistema de presión</t>
+        </is>
+      </c>
+      <c r="F27" s="49" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Laceraciones</t>
+        </is>
+      </c>
+      <c r="G27" s="56" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Influencia</t>
+        </is>
+      </c>
+      <c r="H27" s="57" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1</t>
+        </is>
+      </c>
+      <c r="I27" s="57" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2</t>
+        </is>
+      </c>
       <c r="J27" s="51">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="K27" s="107"/>
-      <c r="L27" s="58"/>
-      <c r="M27" s="58"/>
-      <c r="N27" s="57"/>
-      <c r="O27" s="49"/>
+      <c r="K27" s="107" t="inlineStr">
+        <is>
+          <t xml:space="preserve">inspecciones periódicas</t>
+        </is>
+      </c>
+      <c r="L27" s="58" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Bata/gorro de cuarto limpio (cleanroom), guantes de nitrilo, lentes de seguridad y calzado antiestático (ESD), conforme al ingreso a Cuarto Limpio ISO 7.</t>
+        </is>
+      </c>
+      <c r="M27" s="58" t="inlineStr">
+        <is>
+          <t xml:space="preserve">16-AT40-3318-00013
+16-AT40-3318-00014
+16-AT40-3318-00015
+16-AT40-3318-00016
+16-AT40-3318-00017
+16-AT40-3318-00018
+16-AT40-3318-00019
+16-AT40-3318-00020</t>
+        </is>
+      </c>
+      <c r="N27" s="57" t="inlineStr">
+        <is>
+          <t xml:space="preserve">EHS / Automation</t>
+        </is>
+      </c>
+      <c r="O27" s="49" t="inlineStr">
+        <is>
+          <t xml:space="preserve">5</t>
+        </is>
+      </c>
       <c r="P27" s="61">
         <f t="shared" si="4"/>
         <v>0</v>

--- a/Revalidacion Moose Scorpion Gecko/RA_GECKO.xlsx
+++ b/Revalidacion Moose Scorpion Gecko/RA_GECKO.xlsx
@@ -327,7 +327,7 @@
     <definedName name="Vibracion_herramientas_ctrl">Listas_Controles!$CM$2:$CM$3</definedName>
     <definedName name="Vibracion_herramientas_epp">Listas_EPP!$CJ$2:$CJ$2</definedName>
   </definedNames>
-  <calcPr calcId="191028" fullCalcOnLoad="1"/>
+  <calcPr calcId="191028"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
@@ -6347,7 +6347,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <sheetPr codeName="Sheet1"/>
-  <dimension ref="A1:S33"/>
+  <dimension ref="A1:S46"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="12" bestFit="1" customWidth="1"/>
@@ -6395,7 +6395,7 @@
     <row r="2" spans="1:19" s="20" customFormat="1" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A2" s="145" t="inlineStr">
         <is>
-          <t xml:space="preserve">REVALIDACION: Estaciones GECKO de Atornillado Automático (VSS1H-6050-001 a 006, MS-550-001, MS-550-002)</t>
+          <t xml:space="preserve">REVALIDACION: Estaciones GECKO de Atornillado Automatico (VSS1H-6050-001 a 006, MS-550-001, MS-550-002)</t>
         </is>
       </c>
       <c r="B2" s="127"/>
@@ -6636,7 +6636,7 @@
       </c>
       <c r="H8" s="57" t="inlineStr">
         <is>
-          <t xml:space="preserve">3</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="I8" s="57" t="inlineStr">
@@ -6655,7 +6655,7 @@
       </c>
       <c r="L8" s="58" t="inlineStr">
         <is>
-          <t xml:space="preserve">Bata/gorro de cuarto limpio (cleanroom), guantes de nitrilo, lentes de seguridad y calzado antiestático (ESD), conforme al ingreso a Cuarto Limpio ISO 7.</t>
+          <t xml:space="preserve">Traje de cuarto limpio, cofia, guantes de nitrilo, cubrebocas, lentes de seguridad y calzado antiestático (ESD), conforme al ingreso a Cuarto Limpio ISO 7.</t>
         </is>
       </c>
       <c r="M8" s="58" t="inlineStr">
@@ -6734,11 +6734,11 @@
       </c>
       <c r="I9" s="57" t="inlineStr">
         <is>
-          <t xml:space="preserve">3</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="J9" s="51">
-        <f t="shared" ref="J9:J27" si="3">H9*I9</f>
+        <f t="shared" ref="J9:J46" si="3">H9*I9</f>
         <v>0</v>
       </c>
       <c r="K9" s="107" t="inlineStr">
@@ -6748,7 +6748,7 @@
       </c>
       <c r="L9" s="58" t="inlineStr">
         <is>
-          <t xml:space="preserve">Bata/gorro de cuarto limpio (cleanroom), guantes de nitrilo, lentes de seguridad y calzado antiestático (ESD), conforme al ingreso a Cuarto Limpio ISO 7.</t>
+          <t xml:space="preserve">Traje de cuarto limpio, cofia, guantes de nitrilo, cubrebocas, lentes de seguridad y calzado antiestático (ESD), conforme al ingreso a Cuarto Limpio ISO 7.</t>
         </is>
       </c>
       <c r="M9" s="58" t="inlineStr">
@@ -6774,11 +6774,11 @@
         </is>
       </c>
       <c r="P9" s="61">
-        <f t="shared" ref="P9:P27" si="4">IF(O9=5,(J9*1),IF(O9=4,(J9*0.85),IF(O9=3,(J9*0.15),IF(O9=2,(J9*0.05),IF(O9=1,(J9*-0.0000000000000001),(J9*1))))))</f>
+        <f t="shared" ref="P9:P46" si="4">IF(O9=5,(J9*1),IF(O9=4,(J9*0.85),IF(O9=3,(J9*0.15),IF(O9=2,(J9*0.05),IF(O9=1,(J9*-0.0000000000000001),(J9*1))))))</f>
         <v>0</v>
       </c>
       <c r="Q9" s="60">
-        <f t="shared" ref="Q9:Q27" si="5">IF(J9=0,0,(P9-J9)/J9)</f>
+        <f t="shared" ref="Q9:Q46" si="5">IF(J9=0,0,(P9-J9)/J9)</f>
         <v>0</v>
       </c>
       <c r="R9" s="57"/>
@@ -6797,7 +6797,7 @@
       </c>
       <c r="C10" s="56" t="inlineStr">
         <is>
-          <t xml:space="preserve">El sensor/pin Poka Yoke de la fixtura verifica que la pieza esté correctamente orientada antes de permitir el ciclo; el operador puede tener contacto accidental con el mecanismo al cargar la pieza</t>
+          <t xml:space="preserve">El sensor/pin Poka Yoke de la fixtura verifica la orientación antes de permitir el ciclo; contacto accidental al cargar</t>
         </is>
       </c>
       <c r="D10" s="56" t="inlineStr">
@@ -6841,7 +6841,7 @@
       </c>
       <c r="L10" s="58" t="inlineStr">
         <is>
-          <t xml:space="preserve">Bata/gorro de cuarto limpio (cleanroom), guantes de nitrilo, lentes de seguridad y calzado antiestático (ESD), conforme al ingreso a Cuarto Limpio ISO 7.</t>
+          <t xml:space="preserve">Traje de cuarto limpio, cofia, guantes de nitrilo, cubrebocas, lentes de seguridad y calzado antiestático (ESD), conforme al ingreso a Cuarto Limpio ISO 7.</t>
         </is>
       </c>
       <c r="M10" s="58" t="inlineStr">
@@ -6890,7 +6890,7 @@
       </c>
       <c r="C11" s="56" t="inlineStr">
         <is>
-          <t xml:space="preserve">El escáner fijo lee el código de la pieza/etiqueta antes o durante el ciclo; el operador puede golpearse con el escáner o golpear material al cargar/descargar</t>
+          <t xml:space="preserve">El escáner fijo lee el código de la pieza/etiqueta antes o durante el ciclo</t>
         </is>
       </c>
       <c r="D11" s="56" t="inlineStr">
@@ -6934,7 +6934,7 @@
       </c>
       <c r="L11" s="58" t="inlineStr">
         <is>
-          <t xml:space="preserve">Bata/gorro de cuarto limpio (cleanroom), guantes de nitrilo, lentes de seguridad y calzado antiestático (ESD), conforme al ingreso a Cuarto Limpio ISO 7.</t>
+          <t xml:space="preserve">Traje de cuarto limpio, cofia, guantes de nitrilo, cubrebocas, lentes de seguridad y calzado antiestático (ESD), conforme al ingreso a Cuarto Limpio ISO 7.</t>
         </is>
       </c>
       <c r="M11" s="58" t="inlineStr">
@@ -6983,7 +6983,7 @@
       </c>
       <c r="C12" s="56" t="inlineStr">
         <is>
-          <t xml:space="preserve">El operador puede golpearse o atraparse los dedos con los bordes/topes fijos de la fixtura al colocar o retirar la pieza</t>
+          <t xml:space="preserve">El operador puede golpearse o atraparse los dedos con los bordes/topes fijos de la fixtura</t>
         </is>
       </c>
       <c r="D12" s="56" t="inlineStr">
@@ -7027,7 +7027,7 @@
       </c>
       <c r="L12" s="58" t="inlineStr">
         <is>
-          <t xml:space="preserve">Bata/gorro de cuarto limpio (cleanroom), guantes de nitrilo, lentes de seguridad y calzado antiestático (ESD), conforme al ingreso a Cuarto Limpio ISO 7.</t>
+          <t xml:space="preserve">Traje de cuarto limpio, cofia, guantes de nitrilo, cubrebocas, lentes de seguridad y calzado antiestático (ESD), conforme al ingreso a Cuarto Limpio ISO 7.</t>
         </is>
       </c>
       <c r="M12" s="58" t="inlineStr">
@@ -7071,12 +7071,12 @@
       </c>
       <c r="B13" s="55" t="inlineStr">
         <is>
-          <t xml:space="preserve">Ciclo automático de atornillado (gantry, slider, cabezal de torque)</t>
+          <t xml:space="preserve">Ciclo automático de atornillado - movimiento del gantry/slider</t>
         </is>
       </c>
       <c r="C13" s="56" t="inlineStr">
         <is>
-          <t xml:space="preserve">Paso 1 de 3: el slider mueve la fixtura con la pieza clampeada hacia la posición de atornillado durante el ciclo automático; las cortinas de seguridad del área central impiden el acceso durante este movimiento</t>
+          <t xml:space="preserve">El slider mueve la fixtura con la pieza clampeada hacia la posición de atornillado; las cortinas de seguridad impiden el acceso durante el movimiento</t>
         </is>
       </c>
       <c r="D13" s="56" t="inlineStr">
@@ -7101,7 +7101,7 @@
       </c>
       <c r="H13" s="57" t="inlineStr">
         <is>
-          <t xml:space="preserve">3</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="I13" s="57" t="inlineStr">
@@ -7120,7 +7120,7 @@
       </c>
       <c r="L13" s="58" t="inlineStr">
         <is>
-          <t xml:space="preserve">Bata/gorro de cuarto limpio (cleanroom), guantes de nitrilo, lentes de seguridad y calzado antiestático (ESD), conforme al ingreso a Cuarto Limpio ISO 7.</t>
+          <t xml:space="preserve">Traje de cuarto limpio, cofia, guantes de nitrilo, cubrebocas, lentes de seguridad y calzado antiestático (ESD), conforme al ingreso a Cuarto Limpio ISO 7.</t>
         </is>
       </c>
       <c r="M13" s="58" t="inlineStr">
@@ -7164,12 +7164,12 @@
       </c>
       <c r="B14" s="55" t="inlineStr">
         <is>
-          <t xml:space="preserve">Ciclo automático de atornillado (gantry, slider, cabezal de torque)</t>
+          <t xml:space="preserve">Ciclo automático de atornillado - movimiento del cabezal de torque</t>
         </is>
       </c>
       <c r="C14" s="56" t="inlineStr">
         <is>
-          <t xml:space="preserve">Paso 2 de 3: el cabezal de torque se mueve a la posición del feeder, recoge el tornillo por succión de vacío y se mueve a la posición de atornillado</t>
+          <t xml:space="preserve">El cabezal de torque se mueve a la posición del feeder, recoge el tornillo por succión de vacío y se mueve a la posición de atornillado</t>
         </is>
       </c>
       <c r="D14" s="56" t="inlineStr">
@@ -7194,7 +7194,7 @@
       </c>
       <c r="H14" s="57" t="inlineStr">
         <is>
-          <t xml:space="preserve">3</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="I14" s="57" t="inlineStr">
@@ -7213,7 +7213,7 @@
       </c>
       <c r="L14" s="58" t="inlineStr">
         <is>
-          <t xml:space="preserve">Bata/gorro de cuarto limpio (cleanroom), guantes de nitrilo, lentes de seguridad y calzado antiestático (ESD), conforme al ingreso a Cuarto Limpio ISO 7.</t>
+          <t xml:space="preserve">Traje de cuarto limpio, cofia, guantes de nitrilo, cubrebocas, lentes de seguridad y calzado antiestático (ESD), conforme al ingreso a Cuarto Limpio ISO 7.</t>
         </is>
       </c>
       <c r="M14" s="58" t="inlineStr">
@@ -7257,12 +7257,12 @@
       </c>
       <c r="B15" s="55" t="inlineStr">
         <is>
-          <t xml:space="preserve">Ciclo automático de atornillado (gantry, slider, cabezal de torque)</t>
+          <t xml:space="preserve">Ciclo automático de atornillado - retorno del slider</t>
         </is>
       </c>
       <c r="C15" s="56" t="inlineStr">
         <is>
-          <t xml:space="preserve">Paso 3 de 3: el slider regresa la pieza a la posición frontal para que el operador la descargue</t>
+          <t xml:space="preserve">El slider regresa la pieza a la posición frontal para que el operador la descargue</t>
         </is>
       </c>
       <c r="D15" s="56" t="inlineStr">
@@ -7306,7 +7306,7 @@
       </c>
       <c r="L15" s="58" t="inlineStr">
         <is>
-          <t xml:space="preserve">Bata/gorro de cuarto limpio (cleanroom), guantes de nitrilo, lentes de seguridad y calzado antiestático (ESD), conforme al ingreso a Cuarto Limpio ISO 7.</t>
+          <t xml:space="preserve">Traje de cuarto limpio, cofia, guantes de nitrilo, cubrebocas, lentes de seguridad y calzado antiestático (ESD), conforme al ingreso a Cuarto Limpio ISO 7.</t>
         </is>
       </c>
       <c r="M15" s="58" t="inlineStr">
@@ -7385,7 +7385,7 @@
       </c>
       <c r="I16" s="57" t="inlineStr">
         <is>
-          <t xml:space="preserve">3</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="J16" s="51">
@@ -7399,7 +7399,7 @@
       </c>
       <c r="L16" s="58" t="inlineStr">
         <is>
-          <t xml:space="preserve">Bata/gorro de cuarto limpio (cleanroom), guantes de nitrilo, lentes de seguridad y calzado antiestático (ESD), conforme al ingreso a Cuarto Limpio ISO 7.</t>
+          <t xml:space="preserve">Traje de cuarto limpio, cofia, guantes de nitrilo, cubrebocas, lentes de seguridad y calzado antiestático (ESD), conforme al ingreso a Cuarto Limpio ISO 7.</t>
         </is>
       </c>
       <c r="M16" s="58" t="inlineStr">
@@ -7448,7 +7448,7 @@
       </c>
       <c r="C17" s="56" t="inlineStr">
         <is>
-          <t xml:space="preserve">Las islas/bloques de conexión eléctrica de alimentación y de sensores quedan accesibles en el área de trabajo durante la operación normal</t>
+          <t xml:space="preserve">Las islas/bloques de conexión eléctrica quedan accesibles en el área de trabajo durante la operación normal</t>
         </is>
       </c>
       <c r="D17" s="56" t="inlineStr">
@@ -7492,7 +7492,7 @@
       </c>
       <c r="L17" s="58" t="inlineStr">
         <is>
-          <t xml:space="preserve">Bata/gorro de cuarto limpio (cleanroom), guantes de nitrilo, lentes de seguridad y calzado antiestático (ESD), conforme al ingreso a Cuarto Limpio ISO 7. Adicional para intervención eléctrica: guantes dieléctricos (clase según voltaje) y calzado aislante.</t>
+          <t xml:space="preserve">Traje de cuarto limpio, cofia, guantes de nitrilo, cubrebocas, lentes de seguridad y calzado antiestático (ESD), conforme al ingreso a Cuarto Limpio ISO 7. Adicional para intervención eléctrica: guantes dieléctricos (clase según voltaje) y calzado aislante.</t>
         </is>
       </c>
       <c r="M17" s="58" t="inlineStr">
@@ -7531,32 +7531,32 @@
     <row r="18" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A18" s="55" t="inlineStr">
         <is>
-          <t xml:space="preserve">No rutinario</t>
+          <t xml:space="preserve">Rutinario</t>
         </is>
       </c>
       <c r="B18" s="55" t="inlineStr">
         <is>
-          <t xml:space="preserve">Arranque de la estación al inicio de turno</t>
+          <t xml:space="preserve">Exposición a ruido continuo del equipo en operación</t>
         </is>
       </c>
       <c r="C18" s="56" t="inlineStr">
         <is>
-          <t xml:space="preserve">Paso 1 de 2: energiza el switch general y coloca el switch de llave en modo Automático</t>
+          <t xml:space="preserve">El motor del gantry, el cabezal de torque y el feeder generan ruido continuo durante el ciclo automático</t>
         </is>
       </c>
       <c r="D18" s="56" t="inlineStr">
         <is>
-          <t xml:space="preserve">Eléctrico</t>
+          <t xml:space="preserve">Mecanico</t>
         </is>
       </c>
       <c r="E18" s="49" t="inlineStr">
         <is>
-          <t xml:space="preserve">Conductores energizados</t>
+          <t xml:space="preserve">Ruido</t>
         </is>
       </c>
       <c r="F18" s="49" t="inlineStr">
         <is>
-          <t xml:space="preserve">Electrocución</t>
+          <t xml:space="preserve">Hipoacusia</t>
         </is>
       </c>
       <c r="G18" s="56" t="inlineStr">
@@ -7566,12 +7566,12 @@
       </c>
       <c r="H18" s="57" t="inlineStr">
         <is>
+          <t xml:space="preserve">1</t>
+        </is>
+      </c>
+      <c r="I18" s="57" t="inlineStr">
+        <is>
           <t xml:space="preserve">2</t>
-        </is>
-      </c>
-      <c r="I18" s="57" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="J18" s="51">
@@ -7580,12 +7580,12 @@
       </c>
       <c r="K18" s="107" t="inlineStr">
         <is>
-          <t xml:space="preserve">LOTO</t>
+          <t xml:space="preserve">tapones auditivos</t>
         </is>
       </c>
       <c r="L18" s="58" t="inlineStr">
         <is>
-          <t xml:space="preserve">Bata/gorro de cuarto limpio (cleanroom), guantes de nitrilo, lentes de seguridad y calzado antiestático (ESD), conforme al ingreso a Cuarto Limpio ISO 7. Adicional para intervención eléctrica: guantes dieléctricos (clase según voltaje) y calzado aislante.</t>
+          <t xml:space="preserve">Traje de cuarto limpio, cofia, guantes de nitrilo, cubrebocas, lentes de seguridad y calzado antiestático (ESD), conforme al ingreso a Cuarto Limpio ISO 7. Adicional: protección auditiva (tapones) por exposición a ruido continuo del equipo.</t>
         </is>
       </c>
       <c r="M18" s="58" t="inlineStr">
@@ -7607,7 +7607,7 @@
       </c>
       <c r="O18" s="49" t="inlineStr">
         <is>
-          <t xml:space="preserve">3</t>
+          <t xml:space="preserve">5</t>
         </is>
       </c>
       <c r="P18" s="61">
@@ -7634,22 +7634,22 @@
       </c>
       <c r="C19" s="56" t="inlineStr">
         <is>
-          <t xml:space="preserve">Paso 2 de 2: inicializa el gantry (homing) y verifica que las cortinas de seguridad y el botón de reset funcionen correctamente antes de operar</t>
+          <t xml:space="preserve">Paso 1 de 2: energiza el switch general y coloca el switch de llave en modo Automático</t>
         </is>
       </c>
       <c r="D19" s="56" t="inlineStr">
         <is>
-          <t xml:space="preserve">Mecanico</t>
+          <t xml:space="preserve">Eléctrico</t>
         </is>
       </c>
       <c r="E19" s="49" t="inlineStr">
         <is>
-          <t xml:space="preserve">Partes móviles</t>
+          <t xml:space="preserve">Conductores energizados</t>
         </is>
       </c>
       <c r="F19" s="49" t="inlineStr">
         <is>
-          <t xml:space="preserve">Atrapamiento</t>
+          <t xml:space="preserve">Electrocución</t>
         </is>
       </c>
       <c r="G19" s="56" t="inlineStr">
@@ -7673,15 +7673,108 @@
       </c>
       <c r="K19" s="107" t="inlineStr">
         <is>
+          <t xml:space="preserve">LOTO</t>
+        </is>
+      </c>
+      <c r="L19" s="58" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Traje de cuarto limpio, cofia, guantes de nitrilo, cubrebocas, lentes de seguridad y calzado antiestático (ESD), conforme al ingreso a Cuarto Limpio ISO 7. Adicional para intervención eléctrica: guantes dieléctricos (clase según voltaje) y calzado aislante.</t>
+        </is>
+      </c>
+      <c r="M19" s="58" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Procedimiento LOTO general de la estación: 16-HS20-8000-00017. 16-AT40-3318-00013
+16-AT40-3318-00014
+16-AT40-3318-00015
+16-AT40-3318-00016
+16-AT40-3318-00017
+16-AT40-3318-00018
+16-AT40-3318-00019
+16-AT40-3318-00020</t>
+        </is>
+      </c>
+      <c r="N19" s="57" t="inlineStr">
+        <is>
+          <t xml:space="preserve">EHS / Automation</t>
+        </is>
+      </c>
+      <c r="O19" s="49" t="inlineStr">
+        <is>
+          <t xml:space="preserve">3</t>
+        </is>
+      </c>
+      <c r="P19" s="61">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="Q19" s="60">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="R19" s="57"/>
+      <c r="S19" s="57"/>
+    </row>
+    <row r="20" spans="1:19" x14ac:dyDescent="0.2">
+      <c r="A20" s="55" t="inlineStr">
+        <is>
+          <t xml:space="preserve">No rutinario</t>
+        </is>
+      </c>
+      <c r="B20" s="55" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Arranque de la estación al inicio de turno</t>
+        </is>
+      </c>
+      <c r="C20" s="56" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Paso 2 de 2: inicializa el gantry (homing) y verifica que las cortinas de seguridad y el botón de reset funcionen antes de operar</t>
+        </is>
+      </c>
+      <c r="D20" s="56" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Mecanico</t>
+        </is>
+      </c>
+      <c r="E20" s="49" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Partes móviles</t>
+        </is>
+      </c>
+      <c r="F20" s="49" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Atrapamiento</t>
+        </is>
+      </c>
+      <c r="G20" s="56" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Control</t>
+        </is>
+      </c>
+      <c r="H20" s="57" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2</t>
+        </is>
+      </c>
+      <c r="I20" s="57" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1</t>
+        </is>
+      </c>
+      <c r="J20" s="51">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="K20" s="107" t="inlineStr">
+        <is>
           <t xml:space="preserve">sensores</t>
         </is>
       </c>
-      <c r="L19" s="58" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Bata/gorro de cuarto limpio (cleanroom), guantes de nitrilo, lentes de seguridad y calzado antiestático (ESD), conforme al ingreso a Cuarto Limpio ISO 7.</t>
-        </is>
-      </c>
-      <c r="M19" s="58" t="inlineStr">
+      <c r="L20" s="58" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Traje de cuarto limpio, cofia, guantes de nitrilo, cubrebocas, lentes de seguridad y calzado antiestático (ESD), conforme al ingreso a Cuarto Limpio ISO 7.</t>
+        </is>
+      </c>
+      <c r="M20" s="58" t="inlineStr">
         <is>
           <t xml:space="preserve">16-AT40-3318-00013
 16-AT40-3318-00014
@@ -7693,88 +7786,88 @@
 16-AT40-3318-00020</t>
         </is>
       </c>
-      <c r="N19" s="57" t="inlineStr">
+      <c r="N20" s="57" t="inlineStr">
         <is>
           <t xml:space="preserve">EHS / Automation</t>
         </is>
       </c>
-      <c r="O19" s="49" t="inlineStr">
+      <c r="O20" s="49" t="inlineStr">
         <is>
           <t xml:space="preserve">3</t>
         </is>
       </c>
-      <c r="P19" s="61">
+      <c r="P20" s="61">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
-      <c r="Q19" s="60">
+      <c r="Q20" s="60">
         <f t="shared" si="5"/>
         <v>0</v>
       </c>
-      <c r="R19" s="57"/>
-      <c r="S19" s="57"/>
-    </row>
-    <row r="20" spans="1:19" x14ac:dyDescent="0.2">
-      <c r="A20" s="55" t="inlineStr">
+      <c r="R20" s="57"/>
+      <c r="S20" s="57"/>
+    </row>
+    <row r="21" spans="1:19" x14ac:dyDescent="0.2">
+      <c r="A21" s="55" t="inlineStr">
         <is>
           <t xml:space="preserve">Emergencia </t>
         </is>
       </c>
-      <c r="B20" s="55" t="inlineStr">
+      <c r="B21" s="55" t="inlineStr">
         <is>
           <t xml:space="preserve">Activación del botón de paro de emergencia ante una condición insegura</t>
         </is>
       </c>
-      <c r="C20" s="56" t="inlineStr">
-        <is>
-          <t xml:space="preserve">El operador presiona el botón de paro de emergencia al detectar una condición insegura (atasco de pieza, invasión del área central, ruido anormal) y notifica a su supervisor/mantenimiento</t>
-        </is>
-      </c>
-      <c r="D20" s="56" t="inlineStr">
+      <c r="C21" s="56" t="inlineStr">
+        <is>
+          <t xml:space="preserve">El operador presiona el botón de paro de emergencia al detectar un atasco, invasión del área central o ruido anormal, y notifica a su supervisor</t>
+        </is>
+      </c>
+      <c r="D21" s="56" t="inlineStr">
         <is>
           <t xml:space="preserve">Mecanico</t>
         </is>
       </c>
-      <c r="E20" s="49" t="inlineStr">
+      <c r="E21" s="49" t="inlineStr">
         <is>
           <t xml:space="preserve">Partes móviles</t>
         </is>
       </c>
-      <c r="F20" s="49" t="inlineStr">
+      <c r="F21" s="49" t="inlineStr">
         <is>
           <t xml:space="preserve">Atrapamiento</t>
         </is>
       </c>
-      <c r="G20" s="56" t="inlineStr">
+      <c r="G21" s="56" t="inlineStr">
         <is>
           <t xml:space="preserve">Control</t>
         </is>
       </c>
-      <c r="H20" s="57" t="inlineStr">
+      <c r="H21" s="57" t="inlineStr">
         <is>
           <t xml:space="preserve">1</t>
         </is>
       </c>
-      <c r="I20" s="57" t="inlineStr">
+      <c r="I21" s="57" t="inlineStr">
         <is>
           <t xml:space="preserve">1</t>
         </is>
       </c>
-      <c r="J20" s="51">
+      <c r="J21" s="51">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="K20" s="107" t="inlineStr">
+      <c r="K21" s="107" t="inlineStr">
         <is>
           <t xml:space="preserve">sensores</t>
         </is>
       </c>
-      <c r="L20" s="58" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Bata/gorro de cuarto limpio (cleanroom), guantes de nitrilo, lentes de seguridad y calzado antiestático (ESD), conforme al ingreso a Cuarto Limpio ISO 7.</t>
-        </is>
-      </c>
-      <c r="M20" s="58" t="inlineStr">
+      <c r="L21" s="58" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Traje de cuarto limpio, cofia, guantes de nitrilo, cubrebocas, lentes de seguridad y calzado antiestático (ESD), conforme al ingreso a Cuarto Limpio ISO 7.</t>
+        </is>
+      </c>
+      <c r="M21" s="58" t="inlineStr">
         <is>
           <t xml:space="preserve">16-AT40-3318-00013
 16-AT40-3318-00014
@@ -7786,88 +7879,1390 @@
 16-AT40-3318-00020</t>
         </is>
       </c>
-      <c r="N20" s="57" t="inlineStr">
+      <c r="N21" s="57" t="inlineStr">
         <is>
           <t xml:space="preserve">EHS / Automation</t>
         </is>
       </c>
-      <c r="O20" s="49" t="inlineStr">
+      <c r="O21" s="49" t="inlineStr">
         <is>
           <t xml:space="preserve">3</t>
         </is>
       </c>
-      <c r="P20" s="61">
+      <c r="P21" s="61">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
-      <c r="Q20" s="60">
+      <c r="Q21" s="60">
         <f t="shared" si="5"/>
         <v>0</v>
       </c>
-      <c r="R20" s="57"/>
-      <c r="S20" s="57"/>
-    </row>
-    <row r="21" spans="1:19" x14ac:dyDescent="0.2">
-      <c r="A21" s="55" t="inlineStr">
+      <c r="R21" s="57"/>
+      <c r="S21" s="57"/>
+    </row>
+    <row r="22" spans="1:19" x14ac:dyDescent="0.2">
+      <c r="A22" s="55" t="inlineStr">
         <is>
           <t xml:space="preserve">Emergencia </t>
         </is>
       </c>
-      <c r="B21" s="55" t="inlineStr">
+      <c r="B22" s="55" t="inlineStr">
         <is>
           <t xml:space="preserve">Reinicio del equipo después de un paro de emergencia</t>
         </is>
       </c>
-      <c r="C21" s="56" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Personal autorizado identifica y corrige la causa del paro (ej. libera el atasco con el switch en modo mantenimiento), verifica que el área esté despejada antes de presionar reset y reiniciar el ciclo</t>
-        </is>
-      </c>
-      <c r="D21" s="56" t="inlineStr">
+      <c r="C22" s="56" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Personal autorizado identifica y corrige la causa del paro con el switch en modo mantenimiento, verifica el área despejada y reinicia</t>
+        </is>
+      </c>
+      <c r="D22" s="56" t="inlineStr">
         <is>
           <t xml:space="preserve">Mecanico</t>
         </is>
       </c>
-      <c r="E21" s="49" t="inlineStr">
+      <c r="E22" s="49" t="inlineStr">
         <is>
           <t xml:space="preserve">Partes móviles</t>
         </is>
       </c>
-      <c r="F21" s="49" t="inlineStr">
+      <c r="F22" s="49" t="inlineStr">
         <is>
           <t xml:space="preserve">Atrapamiento</t>
         </is>
       </c>
-      <c r="G21" s="56" t="inlineStr">
+      <c r="G22" s="56" t="inlineStr">
         <is>
           <t xml:space="preserve">Control</t>
         </is>
       </c>
-      <c r="H21" s="57" t="inlineStr">
+      <c r="H22" s="57" t="inlineStr">
         <is>
           <t xml:space="preserve">3</t>
         </is>
       </c>
-      <c r="I21" s="57" t="inlineStr">
+      <c r="I22" s="57" t="inlineStr">
         <is>
           <t xml:space="preserve">1</t>
         </is>
       </c>
-      <c r="J21" s="51">
+      <c r="J22" s="51">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="K21" s="107" t="inlineStr">
+      <c r="K22" s="107" t="inlineStr">
         <is>
           <t xml:space="preserve">LOTO</t>
         </is>
       </c>
-      <c r="L21" s="58" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Bata/gorro de cuarto limpio (cleanroom), guantes de nitrilo, lentes de seguridad y calzado antiestático (ESD), conforme al ingreso a Cuarto Limpio ISO 7.</t>
-        </is>
-      </c>
-      <c r="M21" s="58" t="inlineStr">
+      <c r="L22" s="58" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Traje de cuarto limpio, cofia, guantes de nitrilo, cubrebocas, lentes de seguridad y calzado antiestático (ESD), conforme al ingreso a Cuarto Limpio ISO 7. Adicional para intervención eléctrica: guantes dieléctricos (clase según voltaje) y calzado aislante.</t>
+        </is>
+      </c>
+      <c r="M22" s="58" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Procedimiento LOTO general de la estación: 16-HS20-8000-00017. 16-AT40-3318-00013
+16-AT40-3318-00014
+16-AT40-3318-00015
+16-AT40-3318-00016
+16-AT40-3318-00017
+16-AT40-3318-00018
+16-AT40-3318-00019
+16-AT40-3318-00020</t>
+        </is>
+      </c>
+      <c r="N22" s="57" t="inlineStr">
+        <is>
+          <t xml:space="preserve">EHS / Automation</t>
+        </is>
+      </c>
+      <c r="O22" s="49" t="inlineStr">
+        <is>
+          <t xml:space="preserve">3</t>
+        </is>
+      </c>
+      <c r="P22" s="61">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="Q22" s="60">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="R22" s="57"/>
+      <c r="S22" s="57"/>
+    </row>
+    <row r="23" spans="1:19" x14ac:dyDescent="0.2">
+      <c r="A23" s="55" t="inlineStr">
+        <is>
+          <t xml:space="preserve">No rutinario</t>
+        </is>
+      </c>
+      <c r="B23" s="55" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Mantenimiento mecánico - Cambio de motor del eje X del gantry</t>
+        </is>
+      </c>
+      <c r="C23" s="56" t="inlineStr">
+        <is>
+          <t xml:space="preserve">El personal de mantenimiento bloquea y etiqueta (LOTO) el switch general antes de cambio de motor del eje X del gantry</t>
+        </is>
+      </c>
+      <c r="D23" s="56" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Mecanico</t>
+        </is>
+      </c>
+      <c r="E23" s="49" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Partes móviles</t>
+        </is>
+      </c>
+      <c r="F23" s="49" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Atrapamiento</t>
+        </is>
+      </c>
+      <c r="G23" s="56" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Control</t>
+        </is>
+      </c>
+      <c r="H23" s="57" t="inlineStr">
+        <is>
+          <t xml:space="preserve">5</t>
+        </is>
+      </c>
+      <c r="I23" s="57" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2</t>
+        </is>
+      </c>
+      <c r="J23" s="51">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="K23" s="107" t="inlineStr">
+        <is>
+          <t xml:space="preserve">LOTO</t>
+        </is>
+      </c>
+      <c r="L23" s="58" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Traje de cuarto limpio, cofia, guantes de nitrilo, cubrebocas, lentes de seguridad y calzado antiestático (ESD), conforme al ingreso a Cuarto Limpio ISO 7. Adicional para intervención eléctrica: guantes dieléctricos (clase según voltaje) y calzado aislante.</t>
+        </is>
+      </c>
+      <c r="M23" s="58" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Procedimiento LOTO general de la estación: 16-HS20-8000-00017. 16-AT40-3318-00013
+16-AT40-3318-00014
+16-AT40-3318-00015
+16-AT40-3318-00016
+16-AT40-3318-00017
+16-AT40-3318-00018
+16-AT40-3318-00019
+16-AT40-3318-00020</t>
+        </is>
+      </c>
+      <c r="N23" s="57" t="inlineStr">
+        <is>
+          <t xml:space="preserve">EHS / Automation</t>
+        </is>
+      </c>
+      <c r="O23" s="49" t="inlineStr">
+        <is>
+          <t xml:space="preserve">3</t>
+        </is>
+      </c>
+      <c r="P23" s="61">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="Q23" s="60">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="R23" s="57"/>
+      <c r="S23" s="57"/>
+    </row>
+    <row r="24" spans="1:19" x14ac:dyDescent="0.2">
+      <c r="A24" s="55" t="inlineStr">
+        <is>
+          <t xml:space="preserve">No rutinario</t>
+        </is>
+      </c>
+      <c r="B24" s="55" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Mantenimiento mecánico - Cambio de motor del eje Y del gantry</t>
+        </is>
+      </c>
+      <c r="C24" s="56" t="inlineStr">
+        <is>
+          <t xml:space="preserve">El personal de mantenimiento bloquea y etiqueta (LOTO) el switch general antes de cambio de motor del eje Y del gantry</t>
+        </is>
+      </c>
+      <c r="D24" s="56" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Mecanico</t>
+        </is>
+      </c>
+      <c r="E24" s="49" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Partes móviles</t>
+        </is>
+      </c>
+      <c r="F24" s="49" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Atrapamiento</t>
+        </is>
+      </c>
+      <c r="G24" s="56" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Control</t>
+        </is>
+      </c>
+      <c r="H24" s="57" t="inlineStr">
+        <is>
+          <t xml:space="preserve">5</t>
+        </is>
+      </c>
+      <c r="I24" s="57" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2</t>
+        </is>
+      </c>
+      <c r="J24" s="51">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="K24" s="107" t="inlineStr">
+        <is>
+          <t xml:space="preserve">LOTO</t>
+        </is>
+      </c>
+      <c r="L24" s="58" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Traje de cuarto limpio, cofia, guantes de nitrilo, cubrebocas, lentes de seguridad y calzado antiestático (ESD), conforme al ingreso a Cuarto Limpio ISO 7. Adicional para intervención eléctrica: guantes dieléctricos (clase según voltaje) y calzado aislante.</t>
+        </is>
+      </c>
+      <c r="M24" s="58" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Procedimiento LOTO general de la estación: 16-HS20-8000-00017. 16-AT40-3318-00013
+16-AT40-3318-00014
+16-AT40-3318-00015
+16-AT40-3318-00016
+16-AT40-3318-00017
+16-AT40-3318-00018
+16-AT40-3318-00019
+16-AT40-3318-00020</t>
+        </is>
+      </c>
+      <c r="N24" s="57" t="inlineStr">
+        <is>
+          <t xml:space="preserve">EHS / Automation</t>
+        </is>
+      </c>
+      <c r="O24" s="49" t="inlineStr">
+        <is>
+          <t xml:space="preserve">3</t>
+        </is>
+      </c>
+      <c r="P24" s="61">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="Q24" s="60">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="R24" s="57"/>
+      <c r="S24" s="57"/>
+    </row>
+    <row r="25" spans="1:19" x14ac:dyDescent="0.2">
+      <c r="A25" s="55" t="inlineStr">
+        <is>
+          <t xml:space="preserve">No rutinario</t>
+        </is>
+      </c>
+      <c r="B25" s="55" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Mantenimiento mecánico - Cambio de motor del eje Z (vertical) del gantry</t>
+        </is>
+      </c>
+      <c r="C25" s="56" t="inlineStr">
+        <is>
+          <t xml:space="preserve">El personal de mantenimiento bloquea y etiqueta (LOTO) el switch general antes de cambio de motor del eje Z (vertical) del gantry</t>
+        </is>
+      </c>
+      <c r="D25" s="56" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Mecanico</t>
+        </is>
+      </c>
+      <c r="E25" s="49" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Partes móviles</t>
+        </is>
+      </c>
+      <c r="F25" s="49" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Atrapamiento</t>
+        </is>
+      </c>
+      <c r="G25" s="56" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Control</t>
+        </is>
+      </c>
+      <c r="H25" s="57" t="inlineStr">
+        <is>
+          <t xml:space="preserve">5</t>
+        </is>
+      </c>
+      <c r="I25" s="57" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2</t>
+        </is>
+      </c>
+      <c r="J25" s="51">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="K25" s="107" t="inlineStr">
+        <is>
+          <t xml:space="preserve">LOTO</t>
+        </is>
+      </c>
+      <c r="L25" s="58" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Traje de cuarto limpio, cofia, guantes de nitrilo, cubrebocas, lentes de seguridad y calzado antiestático (ESD), conforme al ingreso a Cuarto Limpio ISO 7. Adicional para intervención eléctrica: guantes dieléctricos (clase según voltaje) y calzado aislante.</t>
+        </is>
+      </c>
+      <c r="M25" s="58" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Procedimiento LOTO general de la estación: 16-HS20-8000-00017. 16-AT40-3318-00013
+16-AT40-3318-00014
+16-AT40-3318-00015
+16-AT40-3318-00016
+16-AT40-3318-00017
+16-AT40-3318-00018
+16-AT40-3318-00019
+16-AT40-3318-00020</t>
+        </is>
+      </c>
+      <c r="N25" s="57" t="inlineStr">
+        <is>
+          <t xml:space="preserve">EHS / Automation</t>
+        </is>
+      </c>
+      <c r="O25" s="49" t="inlineStr">
+        <is>
+          <t xml:space="preserve">3</t>
+        </is>
+      </c>
+      <c r="P25" s="61">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="Q25" s="60">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="R25" s="57"/>
+      <c r="S25" s="57"/>
+    </row>
+    <row r="26" spans="1:19" x14ac:dyDescent="0.2">
+      <c r="A26" s="55" t="inlineStr">
+        <is>
+          <t xml:space="preserve">No rutinario</t>
+        </is>
+      </c>
+      <c r="B26" s="55" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Mantenimiento mecánico - Cambio de motor del slider</t>
+        </is>
+      </c>
+      <c r="C26" s="56" t="inlineStr">
+        <is>
+          <t xml:space="preserve">El personal de mantenimiento bloquea y etiqueta (LOTO) el switch general antes de cambio de motor del slider</t>
+        </is>
+      </c>
+      <c r="D26" s="56" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Mecanico</t>
+        </is>
+      </c>
+      <c r="E26" s="49" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Partes móviles</t>
+        </is>
+      </c>
+      <c r="F26" s="49" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Atrapamiento</t>
+        </is>
+      </c>
+      <c r="G26" s="56" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Control</t>
+        </is>
+      </c>
+      <c r="H26" s="57" t="inlineStr">
+        <is>
+          <t xml:space="preserve">5</t>
+        </is>
+      </c>
+      <c r="I26" s="57" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2</t>
+        </is>
+      </c>
+      <c r="J26" s="51">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="K26" s="107" t="inlineStr">
+        <is>
+          <t xml:space="preserve">LOTO</t>
+        </is>
+      </c>
+      <c r="L26" s="58" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Traje de cuarto limpio, cofia, guantes de nitrilo, cubrebocas, lentes de seguridad y calzado antiestático (ESD), conforme al ingreso a Cuarto Limpio ISO 7. Adicional para intervención eléctrica: guantes dieléctricos (clase según voltaje) y calzado aislante.</t>
+        </is>
+      </c>
+      <c r="M26" s="58" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Procedimiento LOTO general de la estación: 16-HS20-8000-00017. 16-AT40-3318-00013
+16-AT40-3318-00014
+16-AT40-3318-00015
+16-AT40-3318-00016
+16-AT40-3318-00017
+16-AT40-3318-00018
+16-AT40-3318-00019
+16-AT40-3318-00020</t>
+        </is>
+      </c>
+      <c r="N26" s="57" t="inlineStr">
+        <is>
+          <t xml:space="preserve">EHS / Automation</t>
+        </is>
+      </c>
+      <c r="O26" s="49" t="inlineStr">
+        <is>
+          <t xml:space="preserve">3</t>
+        </is>
+      </c>
+      <c r="P26" s="61">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="Q26" s="60">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="R26" s="57"/>
+      <c r="S26" s="57"/>
+    </row>
+    <row r="27" spans="1:19" x14ac:dyDescent="0.2">
+      <c r="A27" s="55" t="inlineStr">
+        <is>
+          <t xml:space="preserve">No rutinario</t>
+        </is>
+      </c>
+      <c r="B27" s="55" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Mantenimiento mecánico - Cambio/ajuste del riel lineal (guía) del gantry</t>
+        </is>
+      </c>
+      <c r="C27" s="56" t="inlineStr">
+        <is>
+          <t xml:space="preserve">El personal de mantenimiento bloquea y etiqueta (LOTO) el switch general antes de cambio/ajuste del riel lineal (guía) del gantry</t>
+        </is>
+      </c>
+      <c r="D27" s="56" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Mecanico</t>
+        </is>
+      </c>
+      <c r="E27" s="49" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Partes móviles</t>
+        </is>
+      </c>
+      <c r="F27" s="49" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Atrapamiento</t>
+        </is>
+      </c>
+      <c r="G27" s="56" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Control</t>
+        </is>
+      </c>
+      <c r="H27" s="57" t="inlineStr">
+        <is>
+          <t xml:space="preserve">4</t>
+        </is>
+      </c>
+      <c r="I27" s="57" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1</t>
+        </is>
+      </c>
+      <c r="J27" s="51">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="K27" s="107" t="inlineStr">
+        <is>
+          <t xml:space="preserve">LOTO</t>
+        </is>
+      </c>
+      <c r="L27" s="58" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Traje de cuarto limpio, cofia, guantes de nitrilo, cubrebocas, lentes de seguridad y calzado antiestático (ESD), conforme al ingreso a Cuarto Limpio ISO 7. Adicional para intervención eléctrica: guantes dieléctricos (clase según voltaje) y calzado aislante.</t>
+        </is>
+      </c>
+      <c r="M27" s="58" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Procedimiento LOTO general de la estación: 16-HS20-8000-00017. 16-AT40-3318-00013
+16-AT40-3318-00014
+16-AT40-3318-00015
+16-AT40-3318-00016
+16-AT40-3318-00017
+16-AT40-3318-00018
+16-AT40-3318-00019
+16-AT40-3318-00020</t>
+        </is>
+      </c>
+      <c r="N27" s="57" t="inlineStr">
+        <is>
+          <t xml:space="preserve">EHS / Automation</t>
+        </is>
+      </c>
+      <c r="O27" s="49" t="inlineStr">
+        <is>
+          <t xml:space="preserve">3</t>
+        </is>
+      </c>
+      <c r="P27" s="61">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="Q27" s="60">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="R27" s="57"/>
+      <c r="S27" s="57"/>
+    </row>
+    <row r="28" spans="1:19" s="19" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A28" s="55" t="inlineStr">
+        <is>
+          <t xml:space="preserve">No rutinario</t>
+        </is>
+      </c>
+      <c r="B28" s="55" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Mantenimiento mecánico - Cambio de correa/banda de transmisión</t>
+        </is>
+      </c>
+      <c r="C28" s="56" t="inlineStr">
+        <is>
+          <t xml:space="preserve">El personal de mantenimiento bloquea y etiqueta (LOTO) el switch general antes de cambio de correa/banda de transmisión</t>
+        </is>
+      </c>
+      <c r="D28" s="56" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Mecanico</t>
+        </is>
+      </c>
+      <c r="E28" s="49" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Partes móviles</t>
+        </is>
+      </c>
+      <c r="F28" s="49" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Atrapamiento</t>
+        </is>
+      </c>
+      <c r="G28" s="56" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Control</t>
+        </is>
+      </c>
+      <c r="H28" s="57" t="inlineStr">
+        <is>
+          <t xml:space="preserve">3</t>
+        </is>
+      </c>
+      <c r="I28" s="57" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2</t>
+        </is>
+      </c>
+      <c r="J28" s="51">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="K28" s="107" t="inlineStr">
+        <is>
+          <t xml:space="preserve">LOTO</t>
+        </is>
+      </c>
+      <c r="L28" s="58" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Traje de cuarto limpio, cofia, guantes de nitrilo, cubrebocas, lentes de seguridad y calzado antiestático (ESD), conforme al ingreso a Cuarto Limpio ISO 7. Adicional para intervención eléctrica: guantes dieléctricos (clase según voltaje) y calzado aislante.</t>
+        </is>
+      </c>
+      <c r="M28" s="58" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Procedimiento LOTO general de la estación: 16-HS20-8000-00017. 16-AT40-3318-00013
+16-AT40-3318-00014
+16-AT40-3318-00015
+16-AT40-3318-00016
+16-AT40-3318-00017
+16-AT40-3318-00018
+16-AT40-3318-00019
+16-AT40-3318-00020</t>
+        </is>
+      </c>
+      <c r="N28" s="57" t="inlineStr">
+        <is>
+          <t xml:space="preserve">EHS / Automation</t>
+        </is>
+      </c>
+      <c r="O28" s="49" t="inlineStr">
+        <is>
+          <t xml:space="preserve">3</t>
+        </is>
+      </c>
+      <c r="P28" s="61">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="Q28" s="60">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="R28" s="57"/>
+      <c r="S28" s="57"/>
+    </row>
+    <row r="29" spans="1:19" s="19" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A29" s="55" t="inlineStr">
+        <is>
+          <t xml:space="preserve">No rutinario</t>
+        </is>
+      </c>
+      <c r="B29" s="55" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Mantenimiento mecánico - Cambio de acoplamiento mecánico del eje</t>
+        </is>
+      </c>
+      <c r="C29" s="56" t="inlineStr">
+        <is>
+          <t xml:space="preserve">El personal de mantenimiento bloquea y etiqueta (LOTO) el switch general antes de cambio de acoplamiento mecánico del eje</t>
+        </is>
+      </c>
+      <c r="D29" s="56" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Mecanico</t>
+        </is>
+      </c>
+      <c r="E29" s="49" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Partes móviles</t>
+        </is>
+      </c>
+      <c r="F29" s="49" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Atrapamiento</t>
+        </is>
+      </c>
+      <c r="G29" s="56" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Control</t>
+        </is>
+      </c>
+      <c r="H29" s="57" t="inlineStr">
+        <is>
+          <t xml:space="preserve">3</t>
+        </is>
+      </c>
+      <c r="I29" s="57" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1</t>
+        </is>
+      </c>
+      <c r="J29" s="51">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="K29" s="107" t="inlineStr">
+        <is>
+          <t xml:space="preserve">LOTO</t>
+        </is>
+      </c>
+      <c r="L29" s="58" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Traje de cuarto limpio, cofia, guantes de nitrilo, cubrebocas, lentes de seguridad y calzado antiestático (ESD), conforme al ingreso a Cuarto Limpio ISO 7. Adicional para intervención eléctrica: guantes dieléctricos (clase según voltaje) y calzado aislante.</t>
+        </is>
+      </c>
+      <c r="M29" s="58" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Procedimiento LOTO general de la estación: 16-HS20-8000-00017. 16-AT40-3318-00013
+16-AT40-3318-00014
+16-AT40-3318-00015
+16-AT40-3318-00016
+16-AT40-3318-00017
+16-AT40-3318-00018
+16-AT40-3318-00019
+16-AT40-3318-00020</t>
+        </is>
+      </c>
+      <c r="N29" s="57" t="inlineStr">
+        <is>
+          <t xml:space="preserve">EHS / Automation</t>
+        </is>
+      </c>
+      <c r="O29" s="49" t="inlineStr">
+        <is>
+          <t xml:space="preserve">3</t>
+        </is>
+      </c>
+      <c r="P29" s="61">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="Q29" s="60">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="R29" s="57"/>
+      <c r="S29" s="57"/>
+    </row>
+    <row r="30" spans="1:19" s="19" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A30" s="55" t="inlineStr">
+        <is>
+          <t xml:space="preserve">No rutinario</t>
+        </is>
+      </c>
+      <c r="B30" s="55" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Mantenimiento mecánico - Cambio de cadena portacables (arrastra-cables)</t>
+        </is>
+      </c>
+      <c r="C30" s="56" t="inlineStr">
+        <is>
+          <t xml:space="preserve">El personal de mantenimiento bloquea y etiqueta (LOTO) el switch general antes de cambio de cadena portacables (arrastra-cables)</t>
+        </is>
+      </c>
+      <c r="D30" s="56" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Mecanico</t>
+        </is>
+      </c>
+      <c r="E30" s="49" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Partes móviles</t>
+        </is>
+      </c>
+      <c r="F30" s="49" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Atrapamiento</t>
+        </is>
+      </c>
+      <c r="G30" s="56" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Control</t>
+        </is>
+      </c>
+      <c r="H30" s="57" t="inlineStr">
+        <is>
+          <t xml:space="preserve">3</t>
+        </is>
+      </c>
+      <c r="I30" s="57" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1</t>
+        </is>
+      </c>
+      <c r="J30" s="51">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="K30" s="107" t="inlineStr">
+        <is>
+          <t xml:space="preserve">LOTO</t>
+        </is>
+      </c>
+      <c r="L30" s="58" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Traje de cuarto limpio, cofia, guantes de nitrilo, cubrebocas, lentes de seguridad y calzado antiestático (ESD), conforme al ingreso a Cuarto Limpio ISO 7. Adicional para intervención eléctrica: guantes dieléctricos (clase según voltaje) y calzado aislante.</t>
+        </is>
+      </c>
+      <c r="M30" s="58" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Procedimiento LOTO general de la estación: 16-HS20-8000-00017. 16-AT40-3318-00013
+16-AT40-3318-00014
+16-AT40-3318-00015
+16-AT40-3318-00016
+16-AT40-3318-00017
+16-AT40-3318-00018
+16-AT40-3318-00019
+16-AT40-3318-00020</t>
+        </is>
+      </c>
+      <c r="N30" s="57" t="inlineStr">
+        <is>
+          <t xml:space="preserve">EHS / Automation</t>
+        </is>
+      </c>
+      <c r="O30" s="49" t="inlineStr">
+        <is>
+          <t xml:space="preserve">3</t>
+        </is>
+      </c>
+      <c r="P30" s="61">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="Q30" s="60">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="R30" s="57"/>
+      <c r="S30" s="57"/>
+    </row>
+    <row r="31" spans="1:19" s="19" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A31" s="55" t="inlineStr">
+        <is>
+          <t xml:space="preserve">No rutinario</t>
+        </is>
+      </c>
+      <c r="B31" s="55" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Mantenimiento mecánico - Ajuste/cambio de encoder</t>
+        </is>
+      </c>
+      <c r="C31" s="56" t="inlineStr">
+        <is>
+          <t xml:space="preserve">El personal de mantenimiento bloquea y etiqueta (LOTO) el switch general antes de ajuste/cambio de encoder</t>
+        </is>
+      </c>
+      <c r="D31" s="56" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Mecanico</t>
+        </is>
+      </c>
+      <c r="E31" s="49" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Partes móviles</t>
+        </is>
+      </c>
+      <c r="F31" s="49" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Atrapamiento</t>
+        </is>
+      </c>
+      <c r="G31" s="56" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Control</t>
+        </is>
+      </c>
+      <c r="H31" s="57" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2</t>
+        </is>
+      </c>
+      <c r="I31" s="57" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1</t>
+        </is>
+      </c>
+      <c r="J31" s="51">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="K31" s="107" t="inlineStr">
+        <is>
+          <t xml:space="preserve">LOTO</t>
+        </is>
+      </c>
+      <c r="L31" s="58" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Traje de cuarto limpio, cofia, guantes de nitrilo, cubrebocas, lentes de seguridad y calzado antiestático (ESD), conforme al ingreso a Cuarto Limpio ISO 7. Adicional para intervención eléctrica: guantes dieléctricos (clase según voltaje) y calzado aislante.</t>
+        </is>
+      </c>
+      <c r="M31" s="58" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Procedimiento LOTO general de la estación: 16-HS20-8000-00017. 16-AT40-3318-00013
+16-AT40-3318-00014
+16-AT40-3318-00015
+16-AT40-3318-00016
+16-AT40-3318-00017
+16-AT40-3318-00018
+16-AT40-3318-00019
+16-AT40-3318-00020</t>
+        </is>
+      </c>
+      <c r="N31" s="57" t="inlineStr">
+        <is>
+          <t xml:space="preserve">EHS / Automation</t>
+        </is>
+      </c>
+      <c r="O31" s="49" t="inlineStr">
+        <is>
+          <t xml:space="preserve">3</t>
+        </is>
+      </c>
+      <c r="P31" s="61">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="Q31" s="60">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="R31" s="57"/>
+      <c r="S31" s="57"/>
+    </row>
+    <row r="32" spans="1:19" s="19" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A32" s="55" t="inlineStr">
+        <is>
+          <t xml:space="preserve">No rutinario</t>
+        </is>
+      </c>
+      <c r="B32" s="55" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Mantenimiento mecánico - Cambio de cabezal de atornillado o bit</t>
+        </is>
+      </c>
+      <c r="C32" s="56" t="inlineStr">
+        <is>
+          <t xml:space="preserve">El personal de mantenimiento bloquea y etiqueta (LOTO) el switch general antes de cambio de cabezal de atornillado o bit</t>
+        </is>
+      </c>
+      <c r="D32" s="56" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Mecanico</t>
+        </is>
+      </c>
+      <c r="E32" s="49" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Partes móviles</t>
+        </is>
+      </c>
+      <c r="F32" s="49" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Atrapamiento</t>
+        </is>
+      </c>
+      <c r="G32" s="56" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Control</t>
+        </is>
+      </c>
+      <c r="H32" s="57" t="inlineStr">
+        <is>
+          <t xml:space="preserve">3</t>
+        </is>
+      </c>
+      <c r="I32" s="57" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2</t>
+        </is>
+      </c>
+      <c r="J32" s="51">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="K32" s="107" t="inlineStr">
+        <is>
+          <t xml:space="preserve">LOTO</t>
+        </is>
+      </c>
+      <c r="L32" s="58" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Traje de cuarto limpio, cofia, guantes de nitrilo, cubrebocas, lentes de seguridad y calzado antiestático (ESD), conforme al ingreso a Cuarto Limpio ISO 7. Adicional para intervención eléctrica: guantes dieléctricos (clase según voltaje) y calzado aislante.</t>
+        </is>
+      </c>
+      <c r="M32" s="58" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Procedimiento LOTO general de la estación: 16-HS20-8000-00017. 16-AT40-3318-00013
+16-AT40-3318-00014
+16-AT40-3318-00015
+16-AT40-3318-00016
+16-AT40-3318-00017
+16-AT40-3318-00018
+16-AT40-3318-00019
+16-AT40-3318-00020</t>
+        </is>
+      </c>
+      <c r="N32" s="57" t="inlineStr">
+        <is>
+          <t xml:space="preserve">EHS / Automation</t>
+        </is>
+      </c>
+      <c r="O32" s="49" t="inlineStr">
+        <is>
+          <t xml:space="preserve">3</t>
+        </is>
+      </c>
+      <c r="P32" s="61">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="Q32" s="60">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="R32" s="57"/>
+      <c r="S32" s="57"/>
+    </row>
+    <row r="33" spans="1:19" s="19" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A33" s="55" t="inlineStr">
+        <is>
+          <t xml:space="preserve">No rutinario</t>
+        </is>
+      </c>
+      <c r="B33" s="55" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Mantenimiento mecánico - Desatasco y limpieza del feeder de tornillos</t>
+        </is>
+      </c>
+      <c r="C33" s="56" t="inlineStr">
+        <is>
+          <t xml:space="preserve">El personal de mantenimiento bloquea y etiqueta (LOTO) el switch general antes de desatasco y limpieza del feeder de tornillos</t>
+        </is>
+      </c>
+      <c r="D33" s="56" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Mecanico</t>
+        </is>
+      </c>
+      <c r="E33" s="49" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Partes móviles</t>
+        </is>
+      </c>
+      <c r="F33" s="49" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Atrapamiento</t>
+        </is>
+      </c>
+      <c r="G33" s="56" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Control</t>
+        </is>
+      </c>
+      <c r="H33" s="57" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2</t>
+        </is>
+      </c>
+      <c r="I33" s="57" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2</t>
+        </is>
+      </c>
+      <c r="J33" s="51">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="K33" s="107" t="inlineStr">
+        <is>
+          <t xml:space="preserve">LOTO</t>
+        </is>
+      </c>
+      <c r="L33" s="58" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Traje de cuarto limpio, cofia, guantes de nitrilo, cubrebocas, lentes de seguridad y calzado antiestático (ESD), conforme al ingreso a Cuarto Limpio ISO 7. Adicional para intervención eléctrica: guantes dieléctricos (clase según voltaje) y calzado aislante.</t>
+        </is>
+      </c>
+      <c r="M33" s="58" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Procedimiento LOTO general de la estación: 16-HS20-8000-00017. 16-AT40-3318-00013
+16-AT40-3318-00014
+16-AT40-3318-00015
+16-AT40-3318-00016
+16-AT40-3318-00017
+16-AT40-3318-00018
+16-AT40-3318-00019
+16-AT40-3318-00020</t>
+        </is>
+      </c>
+      <c r="N33" s="57" t="inlineStr">
+        <is>
+          <t xml:space="preserve">EHS / Automation</t>
+        </is>
+      </c>
+      <c r="O33" s="49" t="inlineStr">
+        <is>
+          <t xml:space="preserve">3</t>
+        </is>
+      </c>
+      <c r="P33" s="61">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="Q33" s="60">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="R33" s="57"/>
+      <c r="S33" s="57"/>
+    </row>
+    <row r="34" spans="1:19" s="19" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A34" s="55" t="inlineStr">
+        <is>
+          <t xml:space="preserve">No rutinario</t>
+        </is>
+      </c>
+      <c r="B34" s="55" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Mantenimiento mecánico - Cambio de boquilla/ventosa de vacío del cabezal</t>
+        </is>
+      </c>
+      <c r="C34" s="56" t="inlineStr">
+        <is>
+          <t xml:space="preserve">El personal de mantenimiento bloquea y etiqueta (LOTO) el switch general antes de cambio de boquilla/ventosa de vacío del cabezal</t>
+        </is>
+      </c>
+      <c r="D34" s="56" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Mecanico</t>
+        </is>
+      </c>
+      <c r="E34" s="49" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Partes móviles</t>
+        </is>
+      </c>
+      <c r="F34" s="49" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Atrapamiento</t>
+        </is>
+      </c>
+      <c r="G34" s="56" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Control</t>
+        </is>
+      </c>
+      <c r="H34" s="57" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2</t>
+        </is>
+      </c>
+      <c r="I34" s="57" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1</t>
+        </is>
+      </c>
+      <c r="J34" s="51">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="K34" s="107" t="inlineStr">
+        <is>
+          <t xml:space="preserve">LOTO</t>
+        </is>
+      </c>
+      <c r="L34" s="58" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Traje de cuarto limpio, cofia, guantes de nitrilo, cubrebocas, lentes de seguridad y calzado antiestático (ESD), conforme al ingreso a Cuarto Limpio ISO 7. Adicional para intervención eléctrica: guantes dieléctricos (clase según voltaje) y calzado aislante.</t>
+        </is>
+      </c>
+      <c r="M34" s="58" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Procedimiento LOTO general de la estación: 16-HS20-8000-00017. 16-AT40-3318-00013
+16-AT40-3318-00014
+16-AT40-3318-00015
+16-AT40-3318-00016
+16-AT40-3318-00017
+16-AT40-3318-00018
+16-AT40-3318-00019
+16-AT40-3318-00020</t>
+        </is>
+      </c>
+      <c r="N34" s="57" t="inlineStr">
+        <is>
+          <t xml:space="preserve">EHS / Automation</t>
+        </is>
+      </c>
+      <c r="O34" s="49" t="inlineStr">
+        <is>
+          <t xml:space="preserve">3</t>
+        </is>
+      </c>
+      <c r="P34" s="61">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="Q34" s="60">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="R34" s="57"/>
+      <c r="S34" s="57"/>
+    </row>
+    <row r="35" spans="1:19" s="19" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A35" s="55" t="inlineStr">
+        <is>
+          <t xml:space="preserve">No rutinario</t>
+        </is>
+      </c>
+      <c r="B35" s="55" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Mantenimiento mecánico - Cambio/ajuste de sensores de límite (fin de carrera)</t>
+        </is>
+      </c>
+      <c r="C35" s="56" t="inlineStr">
+        <is>
+          <t xml:space="preserve">El personal de mantenimiento bloquea y etiqueta (LOTO) el switch general antes de cambio/ajuste de sensores de límite (fin de carrera)</t>
+        </is>
+      </c>
+      <c r="D35" s="56" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Mecanico</t>
+        </is>
+      </c>
+      <c r="E35" s="49" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Partes móviles</t>
+        </is>
+      </c>
+      <c r="F35" s="49" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Atrapamiento</t>
+        </is>
+      </c>
+      <c r="G35" s="56" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Control</t>
+        </is>
+      </c>
+      <c r="H35" s="57" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2</t>
+        </is>
+      </c>
+      <c r="I35" s="57" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1</t>
+        </is>
+      </c>
+      <c r="J35" s="51">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="K35" s="107" t="inlineStr">
+        <is>
+          <t xml:space="preserve">LOTO</t>
+        </is>
+      </c>
+      <c r="L35" s="58" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Traje de cuarto limpio, cofia, guantes de nitrilo, cubrebocas, lentes de seguridad y calzado antiestático (ESD), conforme al ingreso a Cuarto Limpio ISO 7. Adicional para intervención eléctrica: guantes dieléctricos (clase según voltaje) y calzado aislante.</t>
+        </is>
+      </c>
+      <c r="M35" s="58" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Procedimiento LOTO general de la estación: 16-HS20-8000-00017. 16-AT40-3318-00013
+16-AT40-3318-00014
+16-AT40-3318-00015
+16-AT40-3318-00016
+16-AT40-3318-00017
+16-AT40-3318-00018
+16-AT40-3318-00019
+16-AT40-3318-00020</t>
+        </is>
+      </c>
+      <c r="N35" s="57" t="inlineStr">
+        <is>
+          <t xml:space="preserve">EHS / Automation</t>
+        </is>
+      </c>
+      <c r="O35" s="49" t="inlineStr">
+        <is>
+          <t xml:space="preserve">3</t>
+        </is>
+      </c>
+      <c r="P35" s="61">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="Q35" s="60">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="R35" s="57"/>
+      <c r="S35" s="57"/>
+    </row>
+    <row r="36" spans="1:19" s="19" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A36" s="55" t="inlineStr">
+        <is>
+          <t xml:space="preserve">No rutinario</t>
+        </is>
+      </c>
+      <c r="B36" s="55" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Mantenimiento - calibración de la cámara de visión</t>
+        </is>
+      </c>
+      <c r="C36" s="56" t="inlineStr">
+        <is>
+          <t xml:space="preserve">El personal de mantenimiento ajusta/calibra la cámara y el lente del sistema de visión con el equipo bloqueado</t>
+        </is>
+      </c>
+      <c r="D36" s="56" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Ergonomía</t>
+        </is>
+      </c>
+      <c r="E36" s="49" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Movimientos repetitivos</t>
+        </is>
+      </c>
+      <c r="F36" s="49" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Fatiga muscular</t>
+        </is>
+      </c>
+      <c r="G36" s="56" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Influencia</t>
+        </is>
+      </c>
+      <c r="H36" s="57" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1</t>
+        </is>
+      </c>
+      <c r="I36" s="57" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2</t>
+        </is>
+      </c>
+      <c r="J36" s="51">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="K36" s="107" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ergonomía</t>
+        </is>
+      </c>
+      <c r="L36" s="58" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Traje de cuarto limpio, cofia, guantes de nitrilo, cubrebocas, lentes de seguridad y calzado antiestático (ESD), conforme al ingreso a Cuarto Limpio ISO 7.</t>
+        </is>
+      </c>
+      <c r="M36" s="58" t="inlineStr">
         <is>
           <t xml:space="preserve">16-AT40-3318-00013
 16-AT40-3318-00014
@@ -7879,88 +9274,181 @@
 16-AT40-3318-00020</t>
         </is>
       </c>
-      <c r="N21" s="57" t="inlineStr">
+      <c r="N36" s="57" t="inlineStr">
         <is>
           <t xml:space="preserve">EHS / Automation</t>
         </is>
       </c>
-      <c r="O21" s="49" t="inlineStr">
-        <is>
-          <t xml:space="preserve">3</t>
-        </is>
-      </c>
-      <c r="P21" s="61">
+      <c r="O36" s="49" t="inlineStr">
+        <is>
+          <t xml:space="preserve">4</t>
+        </is>
+      </c>
+      <c r="P36" s="61">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
-      <c r="Q21" s="60">
+      <c r="Q36" s="60">
         <f t="shared" si="5"/>
         <v>0</v>
       </c>
-      <c r="R21" s="57"/>
-      <c r="S21" s="57"/>
-    </row>
-    <row r="22" spans="1:19" x14ac:dyDescent="0.2">
-      <c r="A22" s="55" t="inlineStr">
+      <c r="R36" s="57"/>
+      <c r="S36" s="57"/>
+    </row>
+    <row r="37" spans="1:19" s="19" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A37" s="55" t="inlineStr">
         <is>
           <t xml:space="preserve">No rutinario</t>
         </is>
       </c>
-      <c r="B22" s="55" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Mantenimiento mecánico - cambio de motor, eje o cable</t>
-        </is>
-      </c>
-      <c r="C22" s="56" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Paso 1 de 3: cambia el switch de llave a modo Mantenimiento y bloquea/etiqueta el switch general de energía (LOTO) antes de intervenir</t>
-        </is>
-      </c>
-      <c r="D22" s="56" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Mecanico</t>
-        </is>
-      </c>
-      <c r="E22" s="49" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Partes móviles</t>
-        </is>
-      </c>
-      <c r="F22" s="49" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Atrapamiento</t>
-        </is>
-      </c>
-      <c r="G22" s="56" t="inlineStr">
+      <c r="B37" s="55" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Mantenimiento - cambio de iluminación LED del sistema de visión</t>
+        </is>
+      </c>
+      <c r="C37" s="56" t="inlineStr">
+        <is>
+          <t xml:space="preserve">El personal de mantenimiento bloquea el switch general y reemplaza el módulo de iluminación LED</t>
+        </is>
+      </c>
+      <c r="D37" s="56" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Eléctrico</t>
+        </is>
+      </c>
+      <c r="E37" s="49" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Conductores energizados</t>
+        </is>
+      </c>
+      <c r="F37" s="49" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Electrocución</t>
+        </is>
+      </c>
+      <c r="G37" s="56" t="inlineStr">
         <is>
           <t xml:space="preserve">Control</t>
         </is>
       </c>
-      <c r="H22" s="57" t="inlineStr">
-        <is>
-          <t xml:space="preserve">5</t>
-        </is>
-      </c>
-      <c r="I22" s="57" t="inlineStr">
+      <c r="H37" s="57" t="inlineStr">
         <is>
           <t xml:space="preserve">2</t>
         </is>
       </c>
-      <c r="J22" s="51">
+      <c r="I37" s="57" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1</t>
+        </is>
+      </c>
+      <c r="J37" s="51">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="K22" s="107" t="inlineStr">
+      <c r="K37" s="107" t="inlineStr">
         <is>
           <t xml:space="preserve">LOTO</t>
         </is>
       </c>
-      <c r="L22" s="58" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Bata/gorro de cuarto limpio (cleanroom), guantes de nitrilo, lentes de seguridad y calzado antiestático (ESD), conforme al ingreso a Cuarto Limpio ISO 7. Adicional para intervención eléctrica: guantes dieléctricos (clase según voltaje) y calzado aislante.</t>
-        </is>
-      </c>
-      <c r="M22" s="58" t="inlineStr">
+      <c r="L37" s="58" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Traje de cuarto limpio, cofia, guantes de nitrilo, cubrebocas, lentes de seguridad y calzado antiestático (ESD), conforme al ingreso a Cuarto Limpio ISO 7. Adicional para intervención eléctrica: guantes dieléctricos (clase según voltaje) y calzado aislante.</t>
+        </is>
+      </c>
+      <c r="M37" s="58" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Procedimiento LOTO general de la estación: 16-HS20-8000-00017. 16-AT40-3318-00013
+16-AT40-3318-00014
+16-AT40-3318-00015
+16-AT40-3318-00016
+16-AT40-3318-00017
+16-AT40-3318-00018
+16-AT40-3318-00019
+16-AT40-3318-00020</t>
+        </is>
+      </c>
+      <c r="N37" s="57" t="inlineStr">
+        <is>
+          <t xml:space="preserve">EHS / Automation</t>
+        </is>
+      </c>
+      <c r="O37" s="49" t="inlineStr">
+        <is>
+          <t xml:space="preserve">3</t>
+        </is>
+      </c>
+      <c r="P37" s="61">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="Q37" s="60">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="R37" s="57"/>
+      <c r="S37" s="57"/>
+    </row>
+    <row r="38" spans="1:19" s="19" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A38" s="55" t="inlineStr">
+        <is>
+          <t xml:space="preserve">No rutinario</t>
+        </is>
+      </c>
+      <c r="B38" s="55" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Mantenimiento - limpieza/cambio de filtro regulador (FRL) del sistema de vacío</t>
+        </is>
+      </c>
+      <c r="C38" s="56" t="inlineStr">
+        <is>
+          <t xml:space="preserve">El personal de mantenimiento despresuriza la línea antes de intervenir el filtro regulador</t>
+        </is>
+      </c>
+      <c r="D38" s="56" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Mecanico</t>
+        </is>
+      </c>
+      <c r="E38" s="49" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Sistema de presión</t>
+        </is>
+      </c>
+      <c r="F38" s="49" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Laceraciones</t>
+        </is>
+      </c>
+      <c r="G38" s="56" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Control</t>
+        </is>
+      </c>
+      <c r="H38" s="57" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2</t>
+        </is>
+      </c>
+      <c r="I38" s="57" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1</t>
+        </is>
+      </c>
+      <c r="J38" s="51">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="K38" s="107" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Válvulas de alivio</t>
+        </is>
+      </c>
+      <c r="L38" s="58" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Traje de cuarto limpio, cofia, guantes de nitrilo, cubrebocas, lentes de seguridad y calzado antiestático (ESD), conforme al ingreso a Cuarto Limpio ISO 7. Adicional: usar clip de bloqueo neumático tipo C (candado + tarjeta) en el acople rápido de aire.</t>
+        </is>
+      </c>
+      <c r="M38" s="58" t="inlineStr">
         <is>
           <t xml:space="preserve">16-AT40-3318-00013
 16-AT40-3318-00014
@@ -7972,88 +9460,88 @@
 16-AT40-3318-00020</t>
         </is>
       </c>
-      <c r="N22" s="57" t="inlineStr">
+      <c r="N38" s="57" t="inlineStr">
         <is>
           <t xml:space="preserve">EHS / Automation</t>
         </is>
       </c>
-      <c r="O22" s="49" t="inlineStr">
+      <c r="O38" s="49" t="inlineStr">
         <is>
           <t xml:space="preserve">3</t>
         </is>
       </c>
-      <c r="P22" s="61">
+      <c r="P38" s="61">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
-      <c r="Q22" s="60">
+      <c r="Q38" s="60">
         <f t="shared" si="5"/>
         <v>0</v>
       </c>
-      <c r="R22" s="57"/>
-      <c r="S22" s="57"/>
-    </row>
-    <row r="23" spans="1:19" x14ac:dyDescent="0.2">
-      <c r="A23" s="55" t="inlineStr">
+      <c r="R38" s="57"/>
+      <c r="S38" s="57"/>
+    </row>
+    <row r="39" spans="1:19" s="19" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A39" s="55" t="inlineStr">
         <is>
           <t xml:space="preserve">No rutinario</t>
         </is>
       </c>
-      <c r="B23" s="55" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Mantenimiento mecánico - cambio de motor, eje o cable</t>
-        </is>
-      </c>
-      <c r="C23" s="56" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Paso 2 de 3: reemplaza el componente (motor, eje o cable) del gantry/slider/cabezal de torque</t>
-        </is>
-      </c>
-      <c r="D23" s="56" t="inlineStr">
+      <c r="B39" s="55" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Mantenimiento - energía neumática residual del sistema de vacío</t>
+        </is>
+      </c>
+      <c r="C39" s="56" t="inlineStr">
+        <is>
+          <t xml:space="preserve">El personal de mantenimiento interviene la línea neumática de la electroválvula de vacío; riesgo bajo, solo succión de baja presión sin pistones, no existe válvula LOTO neumática dedicada (en evaluación)</t>
+        </is>
+      </c>
+      <c r="D39" s="56" t="inlineStr">
         <is>
           <t xml:space="preserve">Mecanico</t>
         </is>
       </c>
-      <c r="E23" s="49" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Partes móviles</t>
-        </is>
-      </c>
-      <c r="F23" s="49" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Atrapamiento</t>
-        </is>
-      </c>
-      <c r="G23" s="56" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Control</t>
-        </is>
-      </c>
-      <c r="H23" s="57" t="inlineStr">
-        <is>
-          <t xml:space="preserve">4</t>
-        </is>
-      </c>
-      <c r="I23" s="57" t="inlineStr">
+      <c r="E39" s="49" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Sistema de presión</t>
+        </is>
+      </c>
+      <c r="F39" s="49" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Laceraciones</t>
+        </is>
+      </c>
+      <c r="G39" s="56" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Influencia</t>
+        </is>
+      </c>
+      <c r="H39" s="57" t="inlineStr">
         <is>
           <t xml:space="preserve">1</t>
         </is>
       </c>
-      <c r="J23" s="51">
+      <c r="I39" s="57" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2</t>
+        </is>
+      </c>
+      <c r="J39" s="51">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="K23" s="107" t="inlineStr">
-        <is>
-          <t xml:space="preserve">LOTO</t>
-        </is>
-      </c>
-      <c r="L23" s="58" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Bata/gorro de cuarto limpio (cleanroom), guantes de nitrilo, lentes de seguridad y calzado antiestático (ESD), conforme al ingreso a Cuarto Limpio ISO 7.</t>
-        </is>
-      </c>
-      <c r="M23" s="58" t="inlineStr">
+      <c r="K39" s="107" t="inlineStr">
+        <is>
+          <t xml:space="preserve">inspecciones periódicas</t>
+        </is>
+      </c>
+      <c r="L39" s="58" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Traje de cuarto limpio, cofia, guantes de nitrilo, cubrebocas, lentes de seguridad y calzado antiestático (ESD), conforme al ingreso a Cuarto Limpio ISO 7.</t>
+        </is>
+      </c>
+      <c r="M39" s="58" t="inlineStr">
         <is>
           <t xml:space="preserve">16-AT40-3318-00013
 16-AT40-3318-00014
@@ -8065,88 +9553,553 @@
 16-AT40-3318-00020</t>
         </is>
       </c>
-      <c r="N23" s="57" t="inlineStr">
+      <c r="N39" s="57" t="inlineStr">
         <is>
           <t xml:space="preserve">EHS / Automation</t>
         </is>
       </c>
-      <c r="O23" s="49" t="inlineStr">
-        <is>
-          <t xml:space="preserve">3</t>
-        </is>
-      </c>
-      <c r="P23" s="61">
+      <c r="O39" s="49" t="inlineStr">
+        <is>
+          <t xml:space="preserve">5</t>
+        </is>
+      </c>
+      <c r="P39" s="61">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
-      <c r="Q23" s="60">
+      <c r="Q39" s="60">
         <f t="shared" si="5"/>
         <v>0</v>
       </c>
-      <c r="R23" s="57"/>
-      <c r="S23" s="57"/>
-    </row>
-    <row r="24" spans="1:19" x14ac:dyDescent="0.2">
-      <c r="A24" s="55" t="inlineStr">
+      <c r="R39" s="57"/>
+      <c r="S39" s="57"/>
+    </row>
+    <row r="40" spans="1:19" s="19" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A40" s="55" t="inlineStr">
         <is>
           <t xml:space="preserve">No rutinario</t>
         </is>
       </c>
-      <c r="B24" s="55" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Mantenimiento mecánico - cambio de motor, eje o cable</t>
-        </is>
-      </c>
-      <c r="C24" s="56" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Paso 3 de 3: retira el bloqueo LOTO y realiza una prueba funcional del equipo con las cortinas de seguridad activas</t>
-        </is>
-      </c>
-      <c r="D24" s="56" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Mecanico</t>
-        </is>
-      </c>
-      <c r="E24" s="49" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Partes móviles</t>
-        </is>
-      </c>
-      <c r="F24" s="49" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Atrapamiento</t>
-        </is>
-      </c>
-      <c r="G24" s="56" t="inlineStr">
+      <c r="B40" s="55" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Mantenimiento correctivo eléctrico - Cambio de driver/servo del motor</t>
+        </is>
+      </c>
+      <c r="C40" s="56" t="inlineStr">
+        <is>
+          <t xml:space="preserve">El personal de mantenimiento bloquea y etiqueta (LOTO) el switch general, abre el gabinete eléctrico y realiza: cambio de driver/servo del motor</t>
+        </is>
+      </c>
+      <c r="D40" s="56" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Eléctrico</t>
+        </is>
+      </c>
+      <c r="E40" s="49" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Conductores energizados</t>
+        </is>
+      </c>
+      <c r="F40" s="49" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Electrocución</t>
+        </is>
+      </c>
+      <c r="G40" s="56" t="inlineStr">
         <is>
           <t xml:space="preserve">Control</t>
         </is>
       </c>
-      <c r="H24" s="57" t="inlineStr">
-        <is>
-          <t xml:space="preserve">2</t>
-        </is>
-      </c>
-      <c r="I24" s="57" t="inlineStr">
+      <c r="H40" s="57" t="inlineStr">
+        <is>
+          <t xml:space="preserve">5</t>
+        </is>
+      </c>
+      <c r="I40" s="57" t="inlineStr">
         <is>
           <t xml:space="preserve">1</t>
         </is>
       </c>
-      <c r="J24" s="51">
+      <c r="J40" s="51">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="K24" s="107" t="inlineStr">
-        <is>
-          <t xml:space="preserve">sensores</t>
-        </is>
-      </c>
-      <c r="L24" s="58" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Bata/gorro de cuarto limpio (cleanroom), guantes de nitrilo, lentes de seguridad y calzado antiestático (ESD), conforme al ingreso a Cuarto Limpio ISO 7.</t>
-        </is>
-      </c>
-      <c r="M24" s="58" t="inlineStr">
+      <c r="K40" s="107" t="inlineStr">
+        <is>
+          <t xml:space="preserve">LOTO</t>
+        </is>
+      </c>
+      <c r="L40" s="58" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Traje de cuarto limpio, cofia, guantes de nitrilo, cubrebocas, lentes de seguridad y calzado antiestático (ESD), conforme al ingreso a Cuarto Limpio ISO 7. Adicional para intervención eléctrica: guantes dieléctricos (clase según voltaje) y calzado aislante.</t>
+        </is>
+      </c>
+      <c r="M40" s="58" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Procedimiento LOTO general de la estación: 16-HS20-8000-00017. 16-AT40-3318-00013
+16-AT40-3318-00014
+16-AT40-3318-00015
+16-AT40-3318-00016
+16-AT40-3318-00017
+16-AT40-3318-00018
+16-AT40-3318-00019
+16-AT40-3318-00020</t>
+        </is>
+      </c>
+      <c r="N40" s="57" t="inlineStr">
+        <is>
+          <t xml:space="preserve">EHS / Automation</t>
+        </is>
+      </c>
+      <c r="O40" s="49" t="inlineStr">
+        <is>
+          <t xml:space="preserve">3</t>
+        </is>
+      </c>
+      <c r="P40" s="61">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="Q40" s="60">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="R40" s="57"/>
+      <c r="S40" s="57"/>
+    </row>
+    <row r="41" spans="1:19" s="19" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A41" s="55" t="inlineStr">
+        <is>
+          <t xml:space="preserve">No rutinario</t>
+        </is>
+      </c>
+      <c r="B41" s="55" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Mantenimiento correctivo eléctrico - Mantenimiento del PLC / tarjeta de entradas-salidas (I/O)</t>
+        </is>
+      </c>
+      <c r="C41" s="56" t="inlineStr">
+        <is>
+          <t xml:space="preserve">El personal de mantenimiento bloquea y etiqueta (LOTO) el switch general, abre el gabinete eléctrico y realiza: mantenimiento del PLC / tarjeta de entradas-salidas (I/O)</t>
+        </is>
+      </c>
+      <c r="D41" s="56" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Eléctrico</t>
+        </is>
+      </c>
+      <c r="E41" s="49" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Conductores energizados</t>
+        </is>
+      </c>
+      <c r="F41" s="49" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Electrocución</t>
+        </is>
+      </c>
+      <c r="G41" s="56" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Control</t>
+        </is>
+      </c>
+      <c r="H41" s="57" t="inlineStr">
+        <is>
+          <t xml:space="preserve">5</t>
+        </is>
+      </c>
+      <c r="I41" s="57" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1</t>
+        </is>
+      </c>
+      <c r="J41" s="51">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="K41" s="107" t="inlineStr">
+        <is>
+          <t xml:space="preserve">LOTO</t>
+        </is>
+      </c>
+      <c r="L41" s="58" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Traje de cuarto limpio, cofia, guantes de nitrilo, cubrebocas, lentes de seguridad y calzado antiestático (ESD), conforme al ingreso a Cuarto Limpio ISO 7. Adicional para intervención eléctrica: guantes dieléctricos (clase según voltaje) y calzado aislante.</t>
+        </is>
+      </c>
+      <c r="M41" s="58" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Procedimiento LOTO general de la estación: 16-HS20-8000-00017. 16-AT40-3318-00013
+16-AT40-3318-00014
+16-AT40-3318-00015
+16-AT40-3318-00016
+16-AT40-3318-00017
+16-AT40-3318-00018
+16-AT40-3318-00019
+16-AT40-3318-00020</t>
+        </is>
+      </c>
+      <c r="N41" s="57" t="inlineStr">
+        <is>
+          <t xml:space="preserve">EHS / Automation</t>
+        </is>
+      </c>
+      <c r="O41" s="49" t="inlineStr">
+        <is>
+          <t xml:space="preserve">3</t>
+        </is>
+      </c>
+      <c r="P41" s="61">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="Q41" s="60">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="R41" s="57"/>
+      <c r="S41" s="57"/>
+    </row>
+    <row r="42" spans="1:19" s="19" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A42" s="55" t="inlineStr">
+        <is>
+          <t xml:space="preserve">No rutinario</t>
+        </is>
+      </c>
+      <c r="B42" s="55" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Mantenimiento correctivo eléctrico - Cambio de fuente de alimentación</t>
+        </is>
+      </c>
+      <c r="C42" s="56" t="inlineStr">
+        <is>
+          <t xml:space="preserve">El personal de mantenimiento bloquea y etiqueta (LOTO) el switch general, abre el gabinete eléctrico y realiza: cambio de fuente de alimentación</t>
+        </is>
+      </c>
+      <c r="D42" s="56" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Eléctrico</t>
+        </is>
+      </c>
+      <c r="E42" s="49" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Conductores energizados</t>
+        </is>
+      </c>
+      <c r="F42" s="49" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Electrocución</t>
+        </is>
+      </c>
+      <c r="G42" s="56" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Control</t>
+        </is>
+      </c>
+      <c r="H42" s="57" t="inlineStr">
+        <is>
+          <t xml:space="preserve">5</t>
+        </is>
+      </c>
+      <c r="I42" s="57" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1</t>
+        </is>
+      </c>
+      <c r="J42" s="51">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="K42" s="107" t="inlineStr">
+        <is>
+          <t xml:space="preserve">LOTO</t>
+        </is>
+      </c>
+      <c r="L42" s="58" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Traje de cuarto limpio, cofia, guantes de nitrilo, cubrebocas, lentes de seguridad y calzado antiestático (ESD), conforme al ingreso a Cuarto Limpio ISO 7. Adicional para intervención eléctrica: guantes dieléctricos (clase según voltaje) y calzado aislante.</t>
+        </is>
+      </c>
+      <c r="M42" s="58" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Procedimiento LOTO general de la estación: 16-HS20-8000-00017. 16-AT40-3318-00013
+16-AT40-3318-00014
+16-AT40-3318-00015
+16-AT40-3318-00016
+16-AT40-3318-00017
+16-AT40-3318-00018
+16-AT40-3318-00019
+16-AT40-3318-00020</t>
+        </is>
+      </c>
+      <c r="N42" s="57" t="inlineStr">
+        <is>
+          <t xml:space="preserve">EHS / Automation</t>
+        </is>
+      </c>
+      <c r="O42" s="49" t="inlineStr">
+        <is>
+          <t xml:space="preserve">3</t>
+        </is>
+      </c>
+      <c r="P42" s="61">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="Q42" s="60">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="R42" s="57"/>
+      <c r="S42" s="57"/>
+    </row>
+    <row r="43" spans="1:19" s="19" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A43" s="55" t="inlineStr">
+        <is>
+          <t xml:space="preserve">No rutinario</t>
+        </is>
+      </c>
+      <c r="B43" s="55" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Mantenimiento correctivo eléctrico - Revisión/cambio de cableado y conectores</t>
+        </is>
+      </c>
+      <c r="C43" s="56" t="inlineStr">
+        <is>
+          <t xml:space="preserve">El personal de mantenimiento bloquea y etiqueta (LOTO) el switch general, abre el gabinete eléctrico y realiza: revisión/cambio de cableado y conectores</t>
+        </is>
+      </c>
+      <c r="D43" s="56" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Eléctrico</t>
+        </is>
+      </c>
+      <c r="E43" s="49" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Conductores energizados</t>
+        </is>
+      </c>
+      <c r="F43" s="49" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Electrocución</t>
+        </is>
+      </c>
+      <c r="G43" s="56" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Control</t>
+        </is>
+      </c>
+      <c r="H43" s="57" t="inlineStr">
+        <is>
+          <t xml:space="preserve">5</t>
+        </is>
+      </c>
+      <c r="I43" s="57" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1</t>
+        </is>
+      </c>
+      <c r="J43" s="51">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="K43" s="107" t="inlineStr">
+        <is>
+          <t xml:space="preserve">LOTO</t>
+        </is>
+      </c>
+      <c r="L43" s="58" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Traje de cuarto limpio, cofia, guantes de nitrilo, cubrebocas, lentes de seguridad y calzado antiestático (ESD), conforme al ingreso a Cuarto Limpio ISO 7. Adicional para intervención eléctrica: guantes dieléctricos (clase según voltaje) y calzado aislante.</t>
+        </is>
+      </c>
+      <c r="M43" s="58" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Procedimiento LOTO general de la estación: 16-HS20-8000-00017. 16-AT40-3318-00013
+16-AT40-3318-00014
+16-AT40-3318-00015
+16-AT40-3318-00016
+16-AT40-3318-00017
+16-AT40-3318-00018
+16-AT40-3318-00019
+16-AT40-3318-00020</t>
+        </is>
+      </c>
+      <c r="N43" s="57" t="inlineStr">
+        <is>
+          <t xml:space="preserve">EHS / Automation</t>
+        </is>
+      </c>
+      <c r="O43" s="49" t="inlineStr">
+        <is>
+          <t xml:space="preserve">3</t>
+        </is>
+      </c>
+      <c r="P43" s="61">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="Q43" s="60">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="R43" s="57"/>
+      <c r="S43" s="57"/>
+    </row>
+    <row r="44" spans="1:19" s="19" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A44" s="55" t="inlineStr">
+        <is>
+          <t xml:space="preserve">No rutinario</t>
+        </is>
+      </c>
+      <c r="B44" s="55" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Mantenimiento correctivo eléctrico - diagnóstico general de gabinete</t>
+        </is>
+      </c>
+      <c r="C44" s="56" t="inlineStr">
+        <is>
+          <t xml:space="preserve">El personal de mantenimiento abre el panel/gabinete eléctrico de la estación para diagnóstico de falla</t>
+        </is>
+      </c>
+      <c r="D44" s="56" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Eléctrico</t>
+        </is>
+      </c>
+      <c r="E44" s="49" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Conductores energizados</t>
+        </is>
+      </c>
+      <c r="F44" s="49" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Electrocución</t>
+        </is>
+      </c>
+      <c r="G44" s="56" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Control</t>
+        </is>
+      </c>
+      <c r="H44" s="57" t="inlineStr">
+        <is>
+          <t xml:space="preserve">5</t>
+        </is>
+      </c>
+      <c r="I44" s="57" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2</t>
+        </is>
+      </c>
+      <c r="J44" s="51">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="K44" s="107" t="inlineStr">
+        <is>
+          <t xml:space="preserve">LOTO</t>
+        </is>
+      </c>
+      <c r="L44" s="58" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Traje de cuarto limpio, cofia, guantes de nitrilo, cubrebocas, lentes de seguridad y calzado antiestático (ESD), conforme al ingreso a Cuarto Limpio ISO 7. Adicional para intervención eléctrica: guantes dieléctricos (clase según voltaje) y calzado aislante.</t>
+        </is>
+      </c>
+      <c r="M44" s="58" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Procedimiento LOTO general de la estación: 16-HS20-8000-00017. 16-AT40-3318-00013
+16-AT40-3318-00014
+16-AT40-3318-00015
+16-AT40-3318-00016
+16-AT40-3318-00017
+16-AT40-3318-00018
+16-AT40-3318-00019
+16-AT40-3318-00020</t>
+        </is>
+      </c>
+      <c r="N44" s="57" t="inlineStr">
+        <is>
+          <t xml:space="preserve">EHS / Automation</t>
+        </is>
+      </c>
+      <c r="O44" s="49" t="inlineStr">
+        <is>
+          <t xml:space="preserve">3</t>
+        </is>
+      </c>
+      <c r="P44" s="61">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="Q44" s="60">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="R44" s="57"/>
+      <c r="S44" s="57"/>
+    </row>
+    <row r="45" spans="1:19" s="19" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A45" s="55" t="inlineStr">
+        <is>
+          <t xml:space="preserve">No rutinario</t>
+        </is>
+      </c>
+      <c r="B45" s="55" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Uso de herramientas manuales durante ajustes mecánicos</t>
+        </is>
+      </c>
+      <c r="C45" s="56" t="inlineStr">
+        <is>
+          <t xml:space="preserve">El personal de mantenimiento usa llaves, desarmadores y otras herramientas manuales para los ajustes descritos arriba</t>
+        </is>
+      </c>
+      <c r="D45" s="56" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Herramientas</t>
+        </is>
+      </c>
+      <c r="E45" s="49" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Herramientas manuales</t>
+        </is>
+      </c>
+      <c r="F45" s="49" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Golpes</t>
+        </is>
+      </c>
+      <c r="G45" s="56" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Control</t>
+        </is>
+      </c>
+      <c r="H45" s="57" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1</t>
+        </is>
+      </c>
+      <c r="I45" s="57" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1</t>
+        </is>
+      </c>
+      <c r="J45" s="51">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="K45" s="107" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Capacitación</t>
+        </is>
+      </c>
+      <c r="L45" s="58" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Traje de cuarto limpio, cofia, guantes de nitrilo, cubrebocas, lentes de seguridad y calzado antiestático (ESD), conforme al ingreso a Cuarto Limpio ISO 7.</t>
+        </is>
+      </c>
+      <c r="M45" s="58" t="inlineStr">
         <is>
           <t xml:space="preserve">16-AT40-3318-00013
 16-AT40-3318-00014
@@ -8158,88 +10111,88 @@
 16-AT40-3318-00020</t>
         </is>
       </c>
-      <c r="N24" s="57" t="inlineStr">
+      <c r="N45" s="57" t="inlineStr">
         <is>
           <t xml:space="preserve">EHS / Automation</t>
         </is>
       </c>
-      <c r="O24" s="49" t="inlineStr">
-        <is>
-          <t xml:space="preserve">3</t>
-        </is>
-      </c>
-      <c r="P24" s="61">
+      <c r="O45" s="49" t="inlineStr">
+        <is>
+          <t xml:space="preserve">4</t>
+        </is>
+      </c>
+      <c r="P45" s="61">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
-      <c r="Q24" s="60">
+      <c r="Q45" s="60">
         <f t="shared" si="5"/>
         <v>0</v>
       </c>
-      <c r="R24" s="57"/>
-      <c r="S24" s="57"/>
-    </row>
-    <row r="25" spans="1:19" x14ac:dyDescent="0.2">
-      <c r="A25" s="55" t="inlineStr">
+      <c r="R45" s="57"/>
+      <c r="S45" s="57"/>
+    </row>
+    <row r="46" spans="1:19" s="19" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A46" s="55" t="inlineStr">
         <is>
           <t xml:space="preserve">No rutinario</t>
         </is>
       </c>
-      <c r="B25" s="55" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Mantenimiento correctivo eléctrico</t>
-        </is>
-      </c>
-      <c r="C25" s="56" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Paso 1 de 2: bloquea y etiqueta (LOTO) el switch general y abre el gabinete/panel eléctrico de la estación para diagnóstico</t>
-        </is>
-      </c>
-      <c r="D25" s="56" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Eléctrico</t>
-        </is>
-      </c>
-      <c r="E25" s="49" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Conductores energizados</t>
-        </is>
-      </c>
-      <c r="F25" s="49" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Electrocución</t>
-        </is>
-      </c>
-      <c r="G25" s="56" t="inlineStr">
+      <c r="B46" s="55" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Uso de aire comprimido para limpieza del equipo</t>
+        </is>
+      </c>
+      <c r="C46" s="56" t="inlineStr">
+        <is>
+          <t xml:space="preserve">El personal de mantenimiento usa pistola de aire comprimido para limpiar polvo/residuos del gantry, feeder y gabinete</t>
+        </is>
+      </c>
+      <c r="D46" s="56" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Herramientas</t>
+        </is>
+      </c>
+      <c r="E46" s="49" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Partículas expulsadas</t>
+        </is>
+      </c>
+      <c r="F46" s="49" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Lesión ocular</t>
+        </is>
+      </c>
+      <c r="G46" s="56" t="inlineStr">
         <is>
           <t xml:space="preserve">Control</t>
         </is>
       </c>
-      <c r="H25" s="57" t="inlineStr">
-        <is>
-          <t xml:space="preserve">5</t>
-        </is>
-      </c>
-      <c r="I25" s="57" t="inlineStr">
+      <c r="H46" s="57" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1</t>
+        </is>
+      </c>
+      <c r="I46" s="57" t="inlineStr">
         <is>
           <t xml:space="preserve">2</t>
         </is>
       </c>
-      <c r="J25" s="51">
+      <c r="J46" s="51">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="K25" s="107" t="inlineStr">
-        <is>
-          <t xml:space="preserve">LOTO</t>
-        </is>
-      </c>
-      <c r="L25" s="58" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Bata/gorro de cuarto limpio (cleanroom), guantes de nitrilo, lentes de seguridad y calzado antiestático (ESD), conforme al ingreso a Cuarto Limpio ISO 7. Adicional para intervención eléctrica: guantes dieléctricos (clase según voltaje) y calzado aislante.</t>
-        </is>
-      </c>
-      <c r="M25" s="58" t="inlineStr">
+      <c r="K46" s="107" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gafas</t>
+        </is>
+      </c>
+      <c r="L46" s="58" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Traje de cuarto limpio, cofia, guantes de nitrilo, cubrebocas, lentes de seguridad y calzado antiestático (ESD), conforme al ingreso a Cuarto Limpio ISO 7.</t>
+        </is>
+      </c>
+      <c r="M46" s="58" t="inlineStr">
         <is>
           <t xml:space="preserve">16-AT40-3318-00013
 16-AT40-3318-00014
@@ -8251,217 +10204,26 @@
 16-AT40-3318-00020</t>
         </is>
       </c>
-      <c r="N25" s="57" t="inlineStr">
+      <c r="N46" s="57" t="inlineStr">
         <is>
           <t xml:space="preserve">EHS / Automation</t>
         </is>
       </c>
-      <c r="O25" s="49" t="inlineStr">
-        <is>
-          <t xml:space="preserve">3</t>
-        </is>
-      </c>
-      <c r="P25" s="61">
+      <c r="O46" s="49" t="inlineStr">
+        <is>
+          <t xml:space="preserve">4</t>
+        </is>
+      </c>
+      <c r="P46" s="61">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
-      <c r="Q25" s="60">
+      <c r="Q46" s="60">
         <f t="shared" si="5"/>
         <v>0</v>
       </c>
-      <c r="R25" s="57"/>
-      <c r="S25" s="57"/>
-    </row>
-    <row r="26" spans="1:19" x14ac:dyDescent="0.2">
-      <c r="A26" s="55" t="inlineStr">
-        <is>
-          <t xml:space="preserve">No rutinario</t>
-        </is>
-      </c>
-      <c r="B26" s="55" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Mantenimiento correctivo eléctrico</t>
-        </is>
-      </c>
-      <c r="C26" s="56" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Paso 2 de 2: repara o reemplaza el componente dañado, cierra el gabinete y retira el bloqueo LOTO</t>
-        </is>
-      </c>
-      <c r="D26" s="56" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Eléctrico</t>
-        </is>
-      </c>
-      <c r="E26" s="49" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Conductores energizados</t>
-        </is>
-      </c>
-      <c r="F26" s="49" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Electrocución</t>
-        </is>
-      </c>
-      <c r="G26" s="56" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Control</t>
-        </is>
-      </c>
-      <c r="H26" s="57" t="inlineStr">
-        <is>
-          <t xml:space="preserve">5</t>
-        </is>
-      </c>
-      <c r="I26" s="57" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1</t>
-        </is>
-      </c>
-      <c r="J26" s="51">
-        <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-      <c r="K26" s="107" t="inlineStr">
-        <is>
-          <t xml:space="preserve">LOTO</t>
-        </is>
-      </c>
-      <c r="L26" s="58" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Bata/gorro de cuarto limpio (cleanroom), guantes de nitrilo, lentes de seguridad y calzado antiestático (ESD), conforme al ingreso a Cuarto Limpio ISO 7. Adicional para intervención eléctrica: guantes dieléctricos (clase según voltaje) y calzado aislante.</t>
-        </is>
-      </c>
-      <c r="M26" s="58" t="inlineStr">
-        <is>
-          <t xml:space="preserve">16-AT40-3318-00013
-16-AT40-3318-00014
-16-AT40-3318-00015
-16-AT40-3318-00016
-16-AT40-3318-00017
-16-AT40-3318-00018
-16-AT40-3318-00019
-16-AT40-3318-00020</t>
-        </is>
-      </c>
-      <c r="N26" s="57" t="inlineStr">
-        <is>
-          <t xml:space="preserve">EHS / Automation</t>
-        </is>
-      </c>
-      <c r="O26" s="49" t="inlineStr">
-        <is>
-          <t xml:space="preserve">3</t>
-        </is>
-      </c>
-      <c r="P26" s="61">
-        <f t="shared" si="4"/>
-        <v>0</v>
-      </c>
-      <c r="Q26" s="60">
-        <f t="shared" si="5"/>
-        <v>0</v>
-      </c>
-      <c r="R26" s="57"/>
-      <c r="S26" s="57"/>
-    </row>
-    <row r="27" spans="1:19" x14ac:dyDescent="0.2">
-      <c r="A27" s="55" t="inlineStr">
-        <is>
-          <t xml:space="preserve">No rutinario</t>
-        </is>
-      </c>
-      <c r="B27" s="55" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Mantenimiento - energía neumática residual del sistema de vacío</t>
-        </is>
-      </c>
-      <c r="C27" s="56" t="inlineStr">
-        <is>
-          <t xml:space="preserve">El personal de mantenimiento interviene la línea neumática de la electroválvula de vacío; actualmente no existe válvula de despresurización/bloqueo LOTO neumático dedicada (riesgo bajo: solo succión de baja presión, sin pistones)</t>
-        </is>
-      </c>
-      <c r="D27" s="56" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Mecanico</t>
-        </is>
-      </c>
-      <c r="E27" s="49" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Sistema de presión</t>
-        </is>
-      </c>
-      <c r="F27" s="49" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Laceraciones</t>
-        </is>
-      </c>
-      <c r="G27" s="56" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Influencia</t>
-        </is>
-      </c>
-      <c r="H27" s="57" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1</t>
-        </is>
-      </c>
-      <c r="I27" s="57" t="inlineStr">
-        <is>
-          <t xml:space="preserve">2</t>
-        </is>
-      </c>
-      <c r="J27" s="51">
-        <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-      <c r="K27" s="107" t="inlineStr">
-        <is>
-          <t xml:space="preserve">inspecciones periódicas</t>
-        </is>
-      </c>
-      <c r="L27" s="58" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Bata/gorro de cuarto limpio (cleanroom), guantes de nitrilo, lentes de seguridad y calzado antiestático (ESD), conforme al ingreso a Cuarto Limpio ISO 7.</t>
-        </is>
-      </c>
-      <c r="M27" s="58" t="inlineStr">
-        <is>
-          <t xml:space="preserve">16-AT40-3318-00013
-16-AT40-3318-00014
-16-AT40-3318-00015
-16-AT40-3318-00016
-16-AT40-3318-00017
-16-AT40-3318-00018
-16-AT40-3318-00019
-16-AT40-3318-00020</t>
-        </is>
-      </c>
-      <c r="N27" s="57" t="inlineStr">
-        <is>
-          <t xml:space="preserve">EHS / Automation</t>
-        </is>
-      </c>
-      <c r="O27" s="49" t="inlineStr">
-        <is>
-          <t xml:space="preserve">5</t>
-        </is>
-      </c>
-      <c r="P27" s="61">
-        <f t="shared" si="4"/>
-        <v>0</v>
-      </c>
-      <c r="Q27" s="60">
-        <f t="shared" si="5"/>
-        <v>0</v>
-      </c>
-      <c r="R27" s="57"/>
-      <c r="S27" s="57"/>
-    </row>
-    <row r="28" spans="1:19" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="K28" t="s">
-        <v>32</v>
-      </c>
+      <c r="R46" s="57"/>
+      <c r="S46" s="57"/>
     </row>
     <row r="29" spans="1:19" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="30" spans="1:19" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.2"/>
@@ -8505,12 +10267,12 @@
     <mergeCell ref="N4:O4"/>
     <mergeCell ref="E3:G4"/>
   </mergeCells>
-  <conditionalFormatting sqref="J8:J27 P8:P27">
+  <conditionalFormatting sqref="J8:J46 P8:P46">
     <cfRule type="cellIs" dxfId="19" priority="2" operator="equal">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="J8:J27">
+  <conditionalFormatting sqref="J8:J46">
     <cfRule type="cellIs" dxfId="18" priority="7" operator="between">
       <formula>17</formula>
       <formula>25</formula>
@@ -8528,7 +10290,7 @@
       <formula>3</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="P8:P27">
+  <conditionalFormatting sqref="P8:P46">
     <cfRule type="cellIs" dxfId="14" priority="3" operator="between">
       <formula>17</formula>
       <formula>25</formula>
@@ -8553,7 +10315,7 @@
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="G28:G1048576" xr:uid="{00000000-0002-0000-0000-000001000000}">
       <formula1>INDIRECT("Table4[Control-Influencia]")</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H8:I27" xr:uid="{00000000-0002-0000-0000-000002000000}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H8:I46" xr:uid="{00000000-0002-0000-0000-000002000000}">
       <formula1>"1,2,3,4,5"</formula1>
     </dataValidation>
     <dataValidation type="list" allowBlank="1" showDropDown="1" sqref="D28:D500" xr:uid="{00000000-0002-0000-0000-000003000000}">
